--- a/engine/scem_study/SCEM_Valuation_Model_06082026_public.xlsx
+++ b/engine/scem_study/SCEM_Valuation_Model_06082026_public.xlsx
@@ -31,17 +31,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00;(0.00);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.00x"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
-    <numFmt numFmtId="171" formatCode="0.000%"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="172" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,7 +68,6 @@
     <font>
       <b val="1"/>
     </font>
-    <font/>
     <font>
       <color rgb="000000FF"/>
     </font>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,42 +129,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -951,11 +952,11 @@
           <t>Property, plant and equipment (net)</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
-        <v>1451.13582795699</v>
+      <c r="B5" s="22" t="n">
+        <v>2285.624</v>
       </c>
       <c r="C5" s="29">
-        <f>Assumptions!$B$50-C6-C7</f>
+        <f>Assumptions!$B$69-C6-C7</f>
         <v/>
       </c>
       <c r="D5" s="29">
@@ -989,10 +990,10 @@
           <t>Working capital (net)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="22" t="n">
         <v>850</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="22" t="n">
         <v>900</v>
       </c>
       <c r="D6" s="29">
@@ -1026,15 +1027,15 @@
           <t>Cash and equivalents</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
-        <v>1385.443010752688</v>
+      <c r="B7" s="22" t="n">
+        <v>1078</v>
       </c>
       <c r="C7" s="29">
-        <f>'Income Statement'!C10/Assumptions!$B$43</f>
-        <v/>
-      </c>
-      <c r="D7" s="29">
-        <f>C7*Assumptions!$B$44</f>
+        <f>Assumptions!$B$59/1.25</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>Assumptions!$B$59+DCF!B15*Assumptions!$B$56/(1-Assumptions!$B$56)</f>
         <v/>
       </c>
       <c r="E7" s="29">
@@ -1064,35 +1065,35 @@
           <t>Total assets (condensed)</t>
         </is>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>Assumptions!$B$50</f>
-        <v/>
-      </c>
-      <c r="D8" s="32">
+        <f>Assumptions!$B$69</f>
+        <v/>
+      </c>
+      <c r="D8" s="30">
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="30">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="30">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="30">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="30">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -1103,36 +1104,36 @@
           <t>Gross debt</t>
         </is>
       </c>
-      <c r="B9" s="31">
-        <f>Assumptions!$B$17</f>
-        <v/>
-      </c>
-      <c r="C9" s="31">
-        <f>Assumptions!$B$17</f>
-        <v/>
-      </c>
-      <c r="D9" s="31">
-        <f>Assumptions!$B$17</f>
-        <v/>
-      </c>
-      <c r="E9" s="31">
-        <f>Assumptions!$B$17</f>
-        <v/>
-      </c>
-      <c r="F9" s="31">
-        <f>Assumptions!$B$17</f>
-        <v/>
-      </c>
-      <c r="G9" s="31">
-        <f>Assumptions!$B$17</f>
-        <v/>
-      </c>
-      <c r="H9" s="31">
-        <f>Assumptions!$B$17</f>
-        <v/>
-      </c>
-      <c r="I9" s="31">
-        <f>Assumptions!$B$17</f>
+      <c r="B9" s="32">
+        <f>Assumptions!$B$50</f>
+        <v/>
+      </c>
+      <c r="C9" s="32">
+        <f>Assumptions!$B$50</f>
+        <v/>
+      </c>
+      <c r="D9" s="32">
+        <f>Assumptions!$B$50</f>
+        <v/>
+      </c>
+      <c r="E9" s="32">
+        <f>Assumptions!$B$50</f>
+        <v/>
+      </c>
+      <c r="F9" s="32">
+        <f>Assumptions!$B$50</f>
+        <v/>
+      </c>
+      <c r="G9" s="32">
+        <f>Assumptions!$B$50</f>
+        <v/>
+      </c>
+      <c r="H9" s="32">
+        <f>Assumptions!$B$50</f>
+        <v/>
+      </c>
+      <c r="I9" s="32">
+        <f>Assumptions!$B$50</f>
         <v/>
       </c>
     </row>
@@ -1186,7 +1187,7 @@
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>Assumptions!$B$51</f>
+        <f>Assumptions!$B$70</f>
         <v/>
       </c>
       <c r="D11" s="29">
@@ -1220,35 +1221,35 @@
           <t>Shareholders' equity</t>
         </is>
       </c>
-      <c r="B12" s="32">
-        <f>C12-Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
+      <c r="B12" s="30">
+        <f>C12-Assumptions!$B$66</f>
+        <v/>
+      </c>
+      <c r="C12" s="30">
         <f>C8-C11</f>
         <v/>
       </c>
-      <c r="D12" s="32">
-        <f>C12+Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="E12" s="32">
+      <c r="D12" s="26">
+        <f>Assumptions!$B$60</f>
+        <v/>
+      </c>
+      <c r="E12" s="30">
         <f>D12+'Income Statement'!E14-'Cash Flow'!E15</f>
         <v/>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="30">
         <f>E12+'Income Statement'!F14-'Cash Flow'!F15</f>
         <v/>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="30">
         <f>F12+'Income Statement'!G14-'Cash Flow'!G15</f>
         <v/>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="30">
         <f>G12+'Income Statement'!H14-'Cash Flow'!H15</f>
         <v/>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="30">
         <f>H12+'Income Statement'!I14-'Cash Flow'!I15</f>
         <v/>
       </c>
@@ -1259,8 +1260,9 @@
           <t>Equity — reported cross-check</t>
         </is>
       </c>
-      <c r="D13" s="24" t="n">
-        <v>5200</v>
+      <c r="D13" s="29">
+        <f>C12+Assumptions!$B$67</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1309,7 +1311,7 @@
         </is>
       </c>
       <c r="D15" s="12">
-        <f>Assumptions!$C$48/D12</f>
+        <f>Assumptions!$B$67/D12</f>
         <v/>
       </c>
       <c r="E15" s="12">
@@ -1539,23 +1541,23 @@
           <t>Operating free cash flow</t>
         </is>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="30">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="30">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="30">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="30">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -1674,23 +1676,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="30">
         <f>SUM(E9:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="30">
         <f>SUM(F9:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="30">
         <f>SUM(G9:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="30">
         <f>SUM(H9:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="30">
         <f>SUM(I9:I12)</f>
         <v/>
       </c>
@@ -1729,23 +1731,23 @@
         </is>
       </c>
       <c r="E15" s="29">
-        <f>'Income Statement'!E14*Assumptions!$B$42</f>
+        <f>'Income Statement'!E14*Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="F15" s="29">
-        <f>'Income Statement'!F14*Assumptions!$B$42</f>
+        <f>'Income Statement'!F14*Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="G15" s="29">
-        <f>'Income Statement'!G14*Assumptions!$B$42</f>
+        <f>'Income Statement'!G14*Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="H15" s="29">
-        <f>'Income Statement'!H14*Assumptions!$B$42</f>
+        <f>'Income Statement'!H14*Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="I15" s="29">
-        <f>'Income Statement'!I14*Assumptions!$B$42</f>
+        <f>'Income Statement'!I14*Assumptions!$B$41</f>
         <v/>
       </c>
     </row>
@@ -1755,23 +1757,23 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="30">
         <f>'Income Statement'!E14+DCF!B12-DCF!B13-DCF!B14-E15</f>
         <v/>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="30">
         <f>'Income Statement'!F14+DCF!C12-DCF!C13-DCF!C14-F15</f>
         <v/>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="30">
         <f>'Income Statement'!G14+DCF!D12-DCF!D13-DCF!D14-G15</f>
         <v/>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="30">
         <f>'Income Statement'!H14+DCF!E12-DCF!E13-DCF!E14-H15</f>
         <v/>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="30">
         <f>'Income Statement'!I14+DCF!F12-DCF!F13-DCF!F14-I15</f>
         <v/>
       </c>
@@ -2057,35 +2059,35 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>'Unit Build'!B7</f>
+        <f>'Unit Build'!B10</f>
         <v/>
       </c>
       <c r="C9" s="8">
-        <f>'Unit Build'!C7</f>
+        <f>'Unit Build'!C10</f>
         <v/>
       </c>
       <c r="D9" s="8">
-        <f>'Unit Build'!D7</f>
+        <f>'Unit Build'!D10</f>
         <v/>
       </c>
       <c r="E9" s="8">
-        <f>'Unit Build'!E7</f>
+        <f>'Unit Build'!E10</f>
         <v/>
       </c>
       <c r="F9" s="8">
-        <f>'Unit Build'!F7</f>
+        <f>'Unit Build'!F10</f>
         <v/>
       </c>
       <c r="G9" s="8">
-        <f>'Unit Build'!G7</f>
+        <f>'Unit Build'!G10</f>
         <v/>
       </c>
       <c r="H9" s="8">
-        <f>'Unit Build'!H7</f>
+        <f>'Unit Build'!H10</f>
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>'Unit Build'!I7</f>
+        <f>'Unit Build'!I10</f>
         <v/>
       </c>
     </row>
@@ -2096,35 +2098,35 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>'Unit Build'!B9</f>
+        <f>'Unit Build'!B20</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>'Unit Build'!C9</f>
+        <f>'Unit Build'!C20</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>'Unit Build'!D9</f>
+        <f>'Unit Build'!D20</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>'Unit Build'!E9</f>
+        <f>'Unit Build'!E20</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>'Unit Build'!F9</f>
+        <f>'Unit Build'!F20</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>'Unit Build'!G9</f>
+        <f>'Unit Build'!G20</f>
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>'Unit Build'!H9</f>
+        <f>'Unit Build'!H20</f>
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>'Unit Build'!I9</f>
+        <f>'Unit Build'!I20</f>
         <v/>
       </c>
     </row>
@@ -2135,35 +2137,35 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>'Unit Build'!B8</f>
+        <f>'Unit Build'!B6</f>
         <v/>
       </c>
       <c r="C11" s="11">
-        <f>'Unit Build'!C8</f>
+        <f>'Unit Build'!C6</f>
         <v/>
       </c>
       <c r="D11" s="11">
-        <f>'Unit Build'!D8</f>
+        <f>'Unit Build'!D6</f>
         <v/>
       </c>
       <c r="E11" s="11">
-        <f>'Unit Build'!E8</f>
+        <f>'Unit Build'!E6</f>
         <v/>
       </c>
       <c r="F11" s="11">
-        <f>'Unit Build'!F8</f>
+        <f>'Unit Build'!F6</f>
         <v/>
       </c>
       <c r="G11" s="11">
-        <f>'Unit Build'!G8</f>
+        <f>'Unit Build'!G6</f>
         <v/>
       </c>
       <c r="H11" s="11">
-        <f>'Unit Build'!H8</f>
+        <f>'Unit Build'!H6</f>
         <v/>
       </c>
       <c r="I11" s="11">
-        <f>'Unit Build'!I8</f>
+        <f>'Unit Build'!I6</f>
         <v/>
       </c>
     </row>
@@ -2334,27 +2336,27 @@
           <t>1M (1 month)</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>62.1420635589089</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>72.94331198622631</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>80.17497538017265</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="18" t="n">
         <v>88.18397736359992</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <v>103.4995013727537</v>
       </c>
     </row>
@@ -2364,27 +2366,27 @@
           <t>3M (3 months)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="22" t="n">
         <v>62</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>52.12577688877463</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>69.74973064913542</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>82.77876151400348</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="18" t="n">
         <v>98.07395179014382</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="18" t="n">
         <v>131.3522656071748</v>
       </c>
     </row>
@@ -2422,19 +2424,19 @@
           <t>1M</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="20" t="n">
         <v>0.54204</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="20" t="n">
         <v>0.2819</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <v>0.19682</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <v>0.4586</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="20" t="n">
         <v>0.35234</v>
       </c>
     </row>
@@ -2444,19 +2446,19 @@
           <t>3M</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="20" t="n">
         <v>0.5746599999999999</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="20" t="n">
         <v>0.4217</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <v>0.27342</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <v>0.70524</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="F10" s="20" t="n">
         <v>0.56498</v>
       </c>
     </row>
@@ -2475,84 +2477,84 @@
       <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>Market panel verdict (Egypt)</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>PASS — skill +0.0158, 90% interval [0.009, 0.022]</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>This name's verdict</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>PARITY at every bootstrap block size {2,3,4}</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>This name's CRPS skill vs a random walk</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>-0.1276 — BELOW zero</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Coverage 50 / 80 / 90</t>
         </is>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>0.76 / 0.82 / 0.94 against nominal 0.50 / 0.80 / 0.90 — OVER-COVERED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Cone width versus the benchmark</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>4.71x</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>SCEM prints an unchanged close on 29.3% of sessions, 3.4x the Egyptian panel median and 2nd thinnest of 33 names. On such a series the benchmark's own volatility estimate collapses in quiet quarters.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>Consequence</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>The map is ILLUSTRATIVE ONLY. It is materially too wide and must not be read with the confidence of a calibrated name.</t>
         </is>
@@ -2613,7 +2615,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Explicit WACC (rows) × terminal growth (columns) — fair value per share (EGP)</t>
         </is>
@@ -2648,109 +2650,109 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="n">
+      <c r="A6" s="24" t="n">
         <v>0.2529921630262293</v>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>59.01009210696876</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>57.65937496174703</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>56.07012057233603</v>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>54.17302029635631</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>51.86903524268657</v>
+      <c r="B6" s="18" t="n">
+        <v>47.84885020488337</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>46.42439256390911</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>44.78393251379664</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>42.87804730956334</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>40.64083805775741</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n">
+      <c r="A7" s="24" t="n">
         <v>0.2679921630262292</v>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>58.12979307972953</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>56.81386762926719</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>55.26554916327065</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>53.41731428739584</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>51.17267514859882</v>
+      <c r="B7" s="18" t="n">
+        <v>47.27428754847774</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>45.88622828050651</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>44.28766207633895</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>42.43042427686677</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>40.25029345683448</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="n">
+      <c r="A8" s="24" t="n">
         <v>0.2829921630262293</v>
       </c>
-      <c r="B8" s="19" t="n">
-        <v>57.27818372994562</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>55.99586630708646</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>54.48709106120581</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>52.68605910910129</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>50.49874684555345</v>
+      <c r="B8" s="18" t="n">
+        <v>46.71793045432781</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>45.36503894394706</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>43.80695054074625</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>41.99671621018461</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>39.87173537987529</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="n">
+      <c r="A9" s="24" t="n">
         <v>0.2979921630262293</v>
       </c>
-      <c r="B9" s="19" t="n">
-        <v>56.45406278038458</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>55.20422029927338</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>53.7336550841911</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>51.97823462163526</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>49.84631647274035</v>
+      <c r="B9" s="18" t="n">
+        <v>46.17902668304209</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>44.86012465585996</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>43.34115822808959</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>41.5763533327626</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>39.50467604078285</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="24" t="n">
         <v>0.3129921630262292</v>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>55.65629045553789</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>54.43783779326222</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>53.00420585288047</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>51.29287281024559</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>49.2144978281716</v>
+      <c r="B10" s="18" t="n">
+        <v>45.65686220458439</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>44.37082102729465</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>42.88967786277495</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>41.16879466592241</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>39.14865222307241</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
-        <is>
-          <t>Explicit WACC (rows) × terminal WACC (columns) — fair value per share (EGP)</t>
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>NET CASH — the largest single uncertainty, now sensitised</t>
         </is>
       </c>
     </row>
@@ -2758,132 +2760,68 @@
       <c r="A13" s="6" t="inlineStr"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>3,430</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>4,180</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>4,930</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>5,680</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>6,430</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="n">
-        <v>0.2529921630262293</v>
-      </c>
-      <c r="B14" s="19" t="n">
-        <v>60.48610546924424</v>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>58.07360337682618</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>56.07012057233603</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>54.37659482364894</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>52.92368238321455</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>0.2679921630262292</v>
-      </c>
-      <c r="B15" s="19" t="n">
-        <v>59.5644159168212</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>57.21589105821878</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>55.26554916327065</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>53.61695037907413</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>52.20258675295898</v>
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>Fair value per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>38.05569194585932</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>40.93132124330279</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>43.80695054074625</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>46.68257983818972</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>49.55820913563318</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>0.2829921630262293</v>
-      </c>
-      <c r="B16" s="19" t="n">
-        <v>58.67291716058843</v>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>56.38614224680695</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <v>54.48709106120581</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>52.88185493452322</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>51.5046978636255</v>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Revision 1 called net cash the assumption where "an error matters more than</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>0.2979921630262293</v>
-      </c>
-      <c r="B17" s="19" t="n">
-        <v>57.8103406020862</v>
-      </c>
-      <c r="C17" s="19" t="n">
-        <v>55.58318525535164</v>
-      </c>
-      <c r="D17" s="19" t="n">
-        <v>53.7336550841911</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>52.17028537298748</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>50.82905099922696</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>0.3129921630262292</v>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>56.97548275922937</v>
-      </c>
-      <c r="C18" s="19" t="n">
-        <v>54.805908425422</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>53.00420585288047</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <v>51.48127080709907</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>50.17473060797412</v>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>almost any operating assumption", and then published no grid on it. This is that grid.</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>Beta — fair value per share (EGP)</t>
         </is>
@@ -2903,14 +2841,14 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
+          <t>β = 0.84</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
           <t>β = 1.00</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>β = 1.15</t>
-        </is>
-      </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
           <t>β = 1.30</t>
@@ -2918,29 +2856,29 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>Fair value</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
-        <v>61.62711453191083</v>
-      </c>
-      <c r="C22" s="19" t="n">
-        <v>57.68997460982408</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>54.48709106120581</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>52.44698262820113</v>
-      </c>
-      <c r="F22" s="19" t="n">
-        <v>50.65185702135076</v>
+      <c r="B22" s="18" t="n">
+        <v>48.90907393961128</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>46.08371760922441</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>45.62627476231599</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>43.80695054074625</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>41.11738933237334</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>EBITDA margin shift — fair value per share (EGP)</t>
         </is>
@@ -2975,25 +2913,25 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>Fair value</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
-        <v>45.42129736081894</v>
-      </c>
-      <c r="C26" s="19" t="n">
-        <v>49.95419421101236</v>
-      </c>
-      <c r="D26" s="19" t="n">
-        <v>54.48709106120581</v>
-      </c>
-      <c r="E26" s="19" t="n">
-        <v>59.01998791139925</v>
-      </c>
-      <c r="F26" s="19" t="n">
-        <v>63.55288476159266</v>
+      <c r="B26" s="18" t="n">
+        <v>35.56363456632703</v>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>39.6728693813603</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>43.80695054074625</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>47.67547519425753</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>49.79280011722686</v>
       </c>
     </row>
     <row r="28">
@@ -3018,10 +2956,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A30:J30"/>
     <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A16:J16"/>
     <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A30:J30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3331,35 +3271,35 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>'Income Statement'!B6/'Unit Build'!B7</f>
+        <f>'Income Statement'!B6/'Unit Build'!B10</f>
         <v/>
       </c>
       <c r="C11" s="29">
-        <f>'Income Statement'!C6/'Unit Build'!C7</f>
+        <f>'Income Statement'!C6/'Unit Build'!C10</f>
         <v/>
       </c>
       <c r="D11" s="29">
-        <f>'Income Statement'!D6/'Unit Build'!D7</f>
+        <f>'Income Statement'!D6/'Unit Build'!D10</f>
         <v/>
       </c>
       <c r="E11" s="29">
-        <f>'Income Statement'!E6/'Unit Build'!E7</f>
+        <f>'Income Statement'!E6/'Unit Build'!E10</f>
         <v/>
       </c>
       <c r="F11" s="29">
-        <f>'Income Statement'!F6/'Unit Build'!F7</f>
+        <f>'Income Statement'!F6/'Unit Build'!F10</f>
         <v/>
       </c>
       <c r="G11" s="29">
-        <f>'Income Statement'!G6/'Unit Build'!G7</f>
+        <f>'Income Statement'!G6/'Unit Build'!G10</f>
         <v/>
       </c>
       <c r="H11" s="29">
-        <f>'Income Statement'!H6/'Unit Build'!H7</f>
+        <f>'Income Statement'!H6/'Unit Build'!H10</f>
         <v/>
       </c>
       <c r="I11" s="29">
-        <f>'Income Statement'!I6/'Unit Build'!I7</f>
+        <f>'Income Statement'!I6/'Unit Build'!I10</f>
         <v/>
       </c>
     </row>
@@ -3369,35 +3309,35 @@
           <t>Price / earnings (at spot)</t>
         </is>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>Assumptions!$B$5/B5</f>
         <v/>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>Assumptions!$B$5/C5</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>Assumptions!$B$5/D5</f>
         <v/>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>Assumptions!$B$5/E5</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>Assumptions!$B$5/F5</f>
         <v/>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <f>Assumptions!$B$5/G5</f>
         <v/>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="31">
         <f>Assumptions!$B$5/H5</f>
         <v/>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="31">
         <f>Assumptions!$B$5/I5</f>
         <v/>
       </c>
@@ -3408,35 +3348,35 @@
           <t>EV / EBITDA (at spot)</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!B7-'Balance Sheet'!B9))/'Income Statement'!B6</f>
         <v/>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!C7-'Balance Sheet'!C9))/'Income Statement'!C6</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!D7-'Balance Sheet'!D9))/'Income Statement'!D6</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!E7-'Balance Sheet'!E9))/'Income Statement'!E6</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!F7-'Balance Sheet'!F9))/'Income Statement'!F6</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!G7-'Balance Sheet'!G9))/'Income Statement'!G6</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!H7-'Balance Sheet'!H9))/'Income Statement'!H6</f>
         <v/>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!I7-'Balance Sheet'!I9))/'Income Statement'!I6</f>
         <v/>
       </c>
@@ -3511,7 +3451,7 @@
           <t>Misr Beni Suef — FY2025 net sales (EGP mn)</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="22" t="n">
         <v>5700</v>
       </c>
     </row>
@@ -3521,7 +3461,7 @@
           <t>Misr Beni Suef — FY2025 attributable profit (EGP mn)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="22" t="n">
         <v>3946</v>
       </c>
     </row>
@@ -3531,7 +3471,7 @@
           <t>Misr Beni Suef — earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="18" t="n">
         <v>61.25</v>
       </c>
     </row>
@@ -3541,7 +3481,7 @@
           <t>Misr Beni Suef — market capitalisation (EGP mn)</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="22" t="n">
         <v>13730</v>
       </c>
     </row>
@@ -3552,7 +3492,7 @@
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>6.44</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="10">
@@ -3571,7 +3511,7 @@
           <t>Arabian Cement — FY2025 consolidated profit (EGP mn)</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="22" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -3593,7 +3533,7 @@
           <t>Nameplate capacity (Mt/yr)</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="21" t="n">
         <v>76</v>
       </c>
     </row>
@@ -3603,7 +3543,7 @@
           <t>Domestic consumption 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="21" t="n">
         <v>54</v>
       </c>
     </row>
@@ -3613,7 +3553,7 @@
           <t>Production 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="21" t="n">
         <v>65</v>
       </c>
     </row>
@@ -3623,7 +3563,7 @@
           <t>Exports 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="21" t="n">
         <v>18.5</v>
       </c>
     </row>
@@ -3633,7 +3573,7 @@
           <t>Dormant capacity under revival from 2H-2026 (Mt)</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="21" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -3644,7 +3584,7 @@
         </is>
       </c>
       <c r="B19" s="12">
-        <f>Assumptions!$B$8/B14</f>
+        <f>Assumptions!$B$12/B14</f>
         <v/>
       </c>
     </row>
@@ -3665,7 +3605,7 @@
           <t>Structural surplus (capacity less consumption, Mt)</t>
         </is>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="32">
         <f>B14-B15</f>
         <v/>
       </c>
@@ -3676,7 +3616,7 @@
           <t>SCEM EV/EBITDA at spot on FY2026E</t>
         </is>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="31">
         <f>'Per-Share &amp; Ratios'!E13</f>
         <v/>
       </c>
@@ -3962,7 +3902,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>Assumptions!$B$63</f>
+        <f>Assumptions!$B$86</f>
         <v/>
       </c>
     </row>
@@ -4019,7 +3959,7 @@
         </is>
       </c>
       <c r="B25" s="11">
-        <f>Assumptions!$B$24</f>
+        <f>Assumptions!$B$55</f>
         <v/>
       </c>
     </row>
@@ -4122,7 +4062,7 @@
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>Assumptions!$B$66</f>
+        <f>Assumptions!$B$87</f>
         <v/>
       </c>
       <c r="D5" s="15">
@@ -4141,7 +4081,7 @@
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>Assumptions!$B$67</f>
+        <f>Assumptions!$B$88</f>
         <v/>
       </c>
       <c r="D6" s="15">
@@ -4160,7 +4100,7 @@
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>Assumptions!$B$68</f>
+        <f>Assumptions!$B$89</f>
         <v/>
       </c>
       <c r="D7" s="15">
@@ -4179,7 +4119,7 @@
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>Assumptions!$B$69</f>
+        <f>Assumptions!$B$90</f>
         <v/>
       </c>
       <c r="D8" s="15">
@@ -4293,24 +4233,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Assumptions — the drivers</t>
+          <t>Assumptions — every driver, including the whole cost stack</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4325,14 +4265,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Blue cells are inputs. Change one and the model reprices.</t>
+          <t>Blue cells are inputs. Nothing below a driver is typed.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>MARKET AND SHARE COUNT</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B4" s="10" t="n"/>
@@ -4345,79 +4285,69 @@
       <c r="I4" s="10" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Spot price</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="18" t="n">
         <v>79</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>EGP/share, close 06-Aug-2026</t>
+          <t>EGP, close 06-Aug-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Shares outstanding</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="19" t="n">
         <v>260.812477</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>mn — issued capital / EGP 10 par</t>
+          <t>mn</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>Corporate tax rate</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Statutory tax rate</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
         <v>0.225</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Egypt statutory</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>Nameplate capacity</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Effective tax rate (historical closure)</t>
         </is>
       </c>
       <c r="B8" s="20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Mt/yr, two lines</t>
-        </is>
+        <v>0.32</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>USD/EGP</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>USD/EGP (spot)</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
         <v>49.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>COST OF CAPITAL — EXPLICIT WINDOW</t>
+          <t>PLANT — PHYSICAL</t>
         </is>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -4430,189 +4360,184 @@
       <c r="I11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Risk-free rate (EGP 10-year)</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="n">
-        <v>0.2231</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cement grinding capacity</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>3.8</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>observed local-currency yield</t>
+          <t>Mt/yr</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>Sovereign default spread (CDS basis)</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>0.034</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kiln clinker capacity</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>2.57</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>NETTED OUT of rf — no double count</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>Equity risk premium (CDS basis)</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Damodaran, Egypt row</t>
+          <t>Mt/yr</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>tier-3 default on a gate failure</t>
-        </is>
-      </c>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>COST STACK — PHYSICAL AND MARKET DRIVERS</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>Pre-tax cost of debt</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="n">
-        <v>0.215</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Specific thermal energy</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>3.4</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>immaterial — debt is 0.18% of capital</t>
+          <t>GJ/t clinker</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Gross debt</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="n">
-        <v>36.8</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Delivered fuel cost</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>EGP mn</t>
+          <t>USD/GJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Specific electrical energy</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>kWh/t cement</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>COST OF CAPITAL — TERMINAL (norm-built)</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Industrial electricity tariff</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>EGP/kWh</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>Terminal risk-free rate</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="n">
-        <v>0.105</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Raw materials &amp; quarrying</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>190</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>CBE 5% target + 5.5pp real</t>
+          <t>EGP/t cement</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>Terminal equity risk premium</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="n">
-        <v>0.07000000000000001</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>55</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>normalised below crisis level</t>
+          <t>EGP/t bagged</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Terminal cost of debt</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Egyptian corporate norm 14-16%</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bagged share of despatches</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>Terminal debt weight</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="n">
-        <v>0.2</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Distribution &amp; selling</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>250</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>normalised, not today's ~0%</t>
+          <t>EGP/t cement</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="n">
-        <v>0.05</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fixed cash cost</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>14.6</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>EGP nominal; ~0% real</t>
+          <t>USD/t of capacity</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>UNIT BUILD — MARKET SIZE AND SHARE (pasted: research judgement)</t>
+          <t>FORECAST PATHS — FY2025A then FY2026E to FY2030E</t>
         </is>
       </c>
       <c r="B26" s="10" t="n"/>
@@ -4625,152 +4550,212 @@
       <c r="I26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>FY2023 Egyptian consumption / SCEM share</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="n">
-        <v>45</v>
-      </c>
-      <c r="C27" s="21" t="n">
-        <v>0.0449</v>
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FY2024 Egyptian consumption / SCEM share</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="C28" s="21" t="n">
-        <v>0.05</v>
+          <t>Kiln utilisation</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="C28" s="20" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>0.791</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FY2025 Egyptian consumption / SCEM share</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="n">
-        <v>54</v>
-      </c>
-      <c r="C29" s="21" t="n">
-        <v>0.05</v>
+          <t>Domestic share of despatches</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Domestic realised price</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>3503</v>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>3713</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>3880</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>4074</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>4297</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>4512</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>EGP/t</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>FORECAST DRIVERS</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Export price</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="D31" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>FY2027E</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>FY2030E</t>
-        </is>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>USD/EGP path</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>61.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sales volume growth</t>
-        </is>
-      </c>
-      <c r="B33" s="21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C33" s="21" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="D33" s="21" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E33" s="21" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F33" s="21" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Realised price growth (nominal)</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C34" s="21" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="D34" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E34" s="21" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="F34" s="21" t="n">
-        <v>0.051</v>
+          <t>Local cost inflation index</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D33" s="23" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="E33" s="23" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="F33" s="23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="C35" s="21" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="D35" s="21" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E35" s="21" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="F35" s="21" t="n">
-        <v>0.26</v>
-      </c>
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>CAPITAL INTENSITY (FY2026E to FY2030E)</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4778,19 +4763,19 @@
           <t>D&amp;A / revenue</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
+      <c r="B36" s="20" t="n">
         <v>0.046</v>
       </c>
-      <c r="C36" s="21" t="n">
+      <c r="C36" s="20" t="n">
         <v>0.045</v>
       </c>
-      <c r="D36" s="21" t="n">
+      <c r="D36" s="20" t="n">
         <v>0.044</v>
       </c>
-      <c r="E36" s="21" t="n">
+      <c r="E36" s="20" t="n">
         <v>0.043</v>
       </c>
-      <c r="F36" s="21" t="n">
+      <c r="F36" s="20" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -4800,41 +4785,41 @@
           <t>Capex / revenue</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
+      <c r="B37" s="20" t="n">
         <v>0.05</v>
       </c>
-      <c r="C37" s="21" t="n">
+      <c r="C37" s="20" t="n">
         <v>0.048</v>
       </c>
-      <c r="D37" s="21" t="n">
+      <c r="D37" s="20" t="n">
         <v>0.047</v>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="E37" s="20" t="n">
         <v>0.046</v>
       </c>
-      <c r="F37" s="21" t="n">
+      <c r="F37" s="20" t="n">
         <v>0.045</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cost-of-debt path (sets the glide shape)</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="n">
+          <t>Cost-of-debt path</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="n">
         <v>0.215</v>
       </c>
-      <c r="C38" s="21" t="n">
+      <c r="C38" s="20" t="n">
         <v>0.195</v>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="20" t="n">
         <v>0.18</v>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="E38" s="20" t="n">
         <v>0.168</v>
       </c>
-      <c r="F38" s="21" t="n">
+      <c r="F38" s="20" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -4844,408 +4829,619 @@
           <t>Yield earned on cash</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
+      <c r="B39" s="20" t="n">
         <v>0.19</v>
       </c>
-      <c r="C39" s="21" t="n">
+      <c r="C39" s="20" t="n">
         <v>0.17</v>
       </c>
-      <c r="D39" s="21" t="n">
+      <c r="D39" s="20" t="n">
         <v>0.15</v>
       </c>
-      <c r="E39" s="21" t="n">
+      <c r="E39" s="20" t="n">
         <v>0.135</v>
       </c>
-      <c r="F39" s="21" t="n">
+      <c r="F39" s="20" t="n">
         <v>0.125</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Delta working capital / delta revenue</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>Delta working capital / delta revenue</t>
-        </is>
-      </c>
-      <c r="B41" s="21" t="n">
-        <v>0.08</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dividend payout ratio</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>Dividend payout ratio</t>
-        </is>
-      </c>
-      <c r="B42" s="21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>from FY2026E</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Yield on cash, FY2025</t>
         </is>
       </c>
-      <c r="B43" s="21" t="n">
+      <c r="B42" s="20" t="n">
         <v>0.21</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 cash as a multiple of FY2024 cash</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="n">
-        <v>1.35</v>
-      </c>
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>COST OF CAPITAL</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>DISCLOSED HISTORY (pasted: the audited/reported record)</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="10" t="n"/>
-      <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="n"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Risk-free rate (EGP 10-year)</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>0.2231</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FY2023 revenue / profit after tax</t>
+          <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
       <c r="B46" s="24" t="n">
-        <v>4280</v>
-      </c>
-      <c r="C46" s="24" t="n">
-        <v>-121.42</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FY2024 revenue / profit after tax</t>
+          <t>Equity risk premium (CDS basis)</t>
         </is>
       </c>
       <c r="B47" s="24" t="n">
-        <v>6420</v>
-      </c>
-      <c r="C47" s="24" t="n">
-        <v>3070</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FY2025 revenue / profit after tax</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="n">
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="n">
+        <v>0.215</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Gross debt</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Terminal equity risk premium</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Terminal cost of debt</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Terminal debt weight</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Elapsed fraction of FY2026 at valuation</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>BALANCE SHEET AND DISCLOSED HISTORY</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>FY2025 cash (REPORTED)</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>FY2025 equity (reported)</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="n">
+        <v>5240</v>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="n">
+        <v>120</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FY2023 revenue</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="n">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FY2024 revenue</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="n">
+        <v>6420</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FY2025 revenue</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="n">
         <v>9090</v>
       </c>
-      <c r="C48" s="24" t="n">
-        <v>2290</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="18" t="inlineStr">
-        <is>
-          <t>FY2024 EBITDA (the one disclosed margin anchor)</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="n">
-        <v>1590</v>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>FY2024 total assets</t>
-        </is>
-      </c>
-      <c r="B50" s="22" t="n">
-        <v>6385.92</v>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="inlineStr">
-        <is>
-          <t>FY2024 total liabilities</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="n">
-        <v>1610.86</v>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
-        <is>
-          <t>FY2023 treasury income</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="n">
-        <v>198</v>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>Sinai White disposal — EUR consideration</t>
-        </is>
-      </c>
-      <c r="B53" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>EUR mn</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>EGP per EUR at completion</t>
-        </is>
-      </c>
-      <c r="B54" s="22" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Aug-2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="18" t="inlineStr">
-        <is>
-          <t>Sinai White stake — carrying value</t>
-        </is>
-      </c>
-      <c r="B55" s="24" t="n">
-        <v>100</v>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>EGP mn, estimate</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>LENS INPUTS</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="18" t="inlineStr">
-        <is>
-          <t>Replacement cost of capacity</t>
-        </is>
-      </c>
-      <c r="B58" s="24" t="n">
-        <v>130</v>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>USD per annual tonne</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
-        <is>
-          <t>Justified EV per tonne of capacity</t>
-        </is>
-      </c>
-      <c r="B59" s="24" t="n">
-        <v>95</v>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>USD per annual tonne</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B60" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>peer-anchored</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="18" t="inlineStr">
-        <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="B61" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>on normalised earnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="18" t="inlineStr">
-        <is>
-          <t>Mid-cycle EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B62" s="21" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>normalisation lens</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="18" t="inlineStr">
-        <is>
-          <t>Vicat tender offer price</t>
-        </is>
-      </c>
-      <c r="B63" s="19" t="n">
-        <v>41</v>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>disclosed reference, NOT a value</t>
-        </is>
-      </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>LENS WEIGHTS</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="n"/>
-      <c r="C65" s="10" t="n"/>
-      <c r="D65" s="10" t="n"/>
-      <c r="E65" s="10" t="n"/>
-      <c r="F65" s="10" t="n"/>
-      <c r="G65" s="10" t="n"/>
-      <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FY2023 profit after tax</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="n">
+        <v>-121.42</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DCF (cash flow)</t>
-        </is>
-      </c>
-      <c r="B66" s="21" t="n">
-        <v>0.45</v>
+          <t>FY2024 profit after tax</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="n">
+        <v>3070</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Relative multiples</t>
-        </is>
-      </c>
-      <c r="B67" s="21" t="n">
-        <v>0.2</v>
+          <t>FY2025 profit after tax</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="n">
+        <v>2290</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Normalised earnings</t>
-        </is>
-      </c>
-      <c r="B68" s="21" t="n">
-        <v>0.2</v>
+          <t>FY2024 EBITDA (disclosed anchor)</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="n">
+        <v>1590</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Asset / replacement cost</t>
+          <t>FY2024 total assets</t>
         </is>
       </c>
       <c r="B69" s="21" t="n">
-        <v>0.15</v>
+        <v>6385.92</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>FY2024 total liabilities</t>
+        </is>
+      </c>
+      <c r="B70" s="21" t="n">
+        <v>1610.86</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FY2023 treasury income</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FY2023 weighted-average shares</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="n">
+        <v>133.07</v>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FY2024 weighted-average shares</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n">
+        <v>133.07</v>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FY2025 weighted-average shares</t>
+        </is>
+      </c>
+      <c r="B74" s="19" t="n">
+        <v>222</v>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>D&amp;A / revenue, FY2023</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n">
+        <v>0.094</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>D&amp;A / revenue, FY2024</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>D&amp;A / revenue, FY2025</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n">
+        <v>0.046</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>LENS INPUTS AND WEIGHTS</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Replacement cost of capacity</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="n">
+        <v>130</v>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Justified EV per tonne</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="n">
+        <v>95</v>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B82" s="25" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="B83" s="25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Mid-cycle EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B84" s="20" t="n">
+        <v>0.278</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Normalised revenue haircut</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Vicat tender offer price</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Weight — cash flow</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="B88" s="20" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="B89" s="20" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Weight — asset</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>Total (must be 100%)</t>
         </is>
       </c>
-      <c r="B70" s="14">
-        <f>SUM(B66:B69)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Every other sheet references this one. Nothing below a driver is typed.</t>
+      <c r="B91" s="14">
+        <f>SUM(B87:B90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sinai White disposal — EUR consideration</t>
+        </is>
+      </c>
+      <c r="B92" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>EUR mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>EGP per EUR at completion</t>
+        </is>
+      </c>
+      <c r="B93" s="21" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Aug-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sinai White stake — carrying value</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A72:J72"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5396,7 +5592,7 @@
         </is>
       </c>
       <c r="C13" s="7">
-        <f>Assumptions!$B$63</f>
+        <f>Assumptions!$B$86</f>
         <v/>
       </c>
     </row>
@@ -5451,10 +5647,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -5469,7 +5665,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unit build — volume × realised price</t>
+          <t>Bottom-up build — physical units in, EBITDA out</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5485,7 +5681,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Reproduces disclosed revenue by construction.</t>
+          <t>EBITDA is a RESULT of this sheet, never an input.</t>
         </is>
       </c>
     </row>
@@ -5493,40 +5689,30 @@
       <c r="A4" s="6" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025A</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2026E</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2027E</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>FY2026E</t>
+          <t>FY2028E</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>FY2027E</t>
+          <t>FY2029E</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -5535,30 +5721,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian domestic consumption (Mt)</t>
-        </is>
-      </c>
-      <c r="B5" s="27">
-        <f>Assumptions!$B$27</f>
-        <v/>
-      </c>
-      <c r="C5" s="27">
-        <f>Assumptions!$B$28</f>
-        <v/>
-      </c>
-      <c r="D5" s="27">
-        <f>Assumptions!$B$29</f>
+          <t>Kiln clinker capacity (Mt/yr)</t>
+        </is>
+      </c>
+      <c r="B5" s="8">
+        <f>Assumptions!$B$13</f>
+        <v/>
+      </c>
+      <c r="C5" s="8">
+        <f>Assumptions!$B$13</f>
+        <v/>
+      </c>
+      <c r="D5" s="8">
+        <f>Assumptions!$B$13</f>
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>Assumptions!$B$13</f>
+        <v/>
+      </c>
+      <c r="F5" s="8">
+        <f>Assumptions!$B$13</f>
+        <v/>
+      </c>
+      <c r="G5" s="8">
+        <f>Assumptions!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCEM share of market</t>
+          <t>Kiln utilisation</t>
         </is>
       </c>
       <c r="B6" s="11">
-        <f>Assumptions!$C$27</f>
+        <f>Assumptions!$B$28</f>
         <v/>
       </c>
       <c r="C6" s="11">
@@ -5566,238 +5764,976 @@
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>Assumptions!$C$29</f>
+        <f>Assumptions!$D$28</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
+        <f>Assumptions!$E$28</f>
+        <v/>
+      </c>
+      <c r="F6" s="11">
+        <f>Assumptions!$F$28</f>
+        <v/>
+      </c>
+      <c r="G6" s="11">
+        <f>Assumptions!$G$28</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sales volume (Mt)</t>
-        </is>
-      </c>
-      <c r="B7" s="28">
+          <t>Clinker produced (Mt)</t>
+        </is>
+      </c>
+      <c r="B7" s="27">
         <f>B5*B6</f>
         <v/>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="27">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="27">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="28">
-        <f>D7*(1+Assumptions!$B$33)</f>
-        <v/>
-      </c>
-      <c r="F7" s="28">
-        <f>E7*(1+Assumptions!$C$33)</f>
-        <v/>
-      </c>
-      <c r="G7" s="28">
-        <f>F7*(1+Assumptions!$D$33)</f>
-        <v/>
-      </c>
-      <c r="H7" s="28">
-        <f>G7*(1+Assumptions!$E$33)</f>
-        <v/>
-      </c>
-      <c r="I7" s="28">
-        <f>H7*(1+Assumptions!$F$33)</f>
+      <c r="E7" s="27">
+        <f>E5*E6</f>
+        <v/>
+      </c>
+      <c r="F7" s="27">
+        <f>F5*F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="27">
+        <f>G5*G6</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Capacity utilisation</t>
-        </is>
-      </c>
-      <c r="B8" s="12">
-        <f>B7/Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="C8" s="12">
-        <f>C7/Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="D8" s="12">
-        <f>D7/Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="E8" s="12">
-        <f>E7/Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
-        <f>F7/Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="G8" s="12">
-        <f>G7/Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="H8" s="12">
-        <f>H7/Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="I8" s="12">
-        <f>I7/Assumptions!$B$8</f>
+          <t>Cement grinding capacity (Mt/yr)</t>
+        </is>
+      </c>
+      <c r="B8" s="8">
+        <f>Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="C8" s="8">
+        <f>Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="D8" s="8">
+        <f>Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="F8" s="8">
+        <f>Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="G8" s="8">
+        <f>Assumptions!$B$12</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Realised price (EGP/t)</t>
-        </is>
-      </c>
-      <c r="B9" s="29">
-        <f>B11/B7</f>
-        <v/>
-      </c>
-      <c r="C9" s="29">
-        <f>C11/C7</f>
-        <v/>
-      </c>
-      <c r="D9" s="29">
-        <f>D11/D7</f>
-        <v/>
-      </c>
-      <c r="E9" s="29">
-        <f>D9*(1+Assumptions!$B$34)</f>
-        <v/>
-      </c>
-      <c r="F9" s="29">
-        <f>E9*(1+Assumptions!$C$34)</f>
-        <v/>
-      </c>
-      <c r="G9" s="29">
-        <f>F9*(1+Assumptions!$D$34)</f>
-        <v/>
-      </c>
-      <c r="H9" s="29">
-        <f>G9*(1+Assumptions!$E$34)</f>
-        <v/>
-      </c>
-      <c r="I9" s="29">
-        <f>H9*(1+Assumptions!$F$34)</f>
+          <t>Clinker factor (t clinker / t cement)</t>
+        </is>
+      </c>
+      <c r="B9" s="27">
+        <f>B5/B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="27">
+        <f>C5/C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="27">
+        <f>D5/D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="27">
+        <f>E5/E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="27">
+        <f>F5/F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="27">
+        <f>G5/G8</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B10" s="29">
-        <f>B7*B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="29">
-        <f>C7*C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="29">
-        <f>D7*D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="29">
-        <f>E7*E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="29">
-        <f>F7*F9</f>
-        <v/>
-      </c>
-      <c r="G10" s="29">
-        <f>G7*G9</f>
-        <v/>
-      </c>
-      <c r="H10" s="29">
-        <f>H7*H9</f>
-        <v/>
-      </c>
-      <c r="I10" s="29">
-        <f>I7*I9</f>
+          <t>Cement produced (Mt)</t>
+        </is>
+      </c>
+      <c r="B10" s="27">
+        <f>B7/B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="27">
+        <f>C7/C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>D7/D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>E7/E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="27">
+        <f>F7/F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="27">
+        <f>G7/G9</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Revenue — disclosed (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B11" s="9">
-        <f>Assumptions!$B$46</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
-        <f>Assumptions!$B$47</f>
-        <v/>
-      </c>
-      <c r="D11" s="9">
-        <f>Assumptions!$B$48</f>
+          <t>Domestic share</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="C11" s="11">
+        <f>Assumptions!$C$29</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>Assumptions!$D$29</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>Assumptions!$E$29</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>Assumptions!$F$29</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
+        <f>Assumptions!$G$29</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Check: build less disclosed</t>
-        </is>
-      </c>
-      <c r="B12" s="28">
-        <f>B10-B11</f>
-        <v/>
-      </c>
-      <c r="C12" s="28">
-        <f>C10-C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="28">
-        <f>D10-D11</f>
+          <t>Domestic volume (Mt)</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>B10*B11</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>C10*C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>D10*D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>E10*E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>F10*F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>G10*G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Export volume (Mt)</t>
+        </is>
+      </c>
+      <c r="B13" s="27">
+        <f>B10-B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="27">
+        <f>C10-C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>D10-D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="27">
+        <f>E10-E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="27">
+        <f>F10-F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="27">
+        <f>G10-G12</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Historical volume = market size × share (both pasted research judgements); realised price is</t>
-        </is>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Domestic price (EGP/t)</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="C14" s="9">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="D14" s="9">
+        <f>Assumptions!$D$30</f>
+        <v/>
+      </c>
+      <c r="E14" s="9">
+        <f>Assumptions!$E$30</f>
+        <v/>
+      </c>
+      <c r="F14" s="9">
+        <f>Assumptions!$F$30</f>
+        <v/>
+      </c>
+      <c r="G14" s="9">
+        <f>Assumptions!$G$30</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>then SOLVED as disclosed revenue ÷ volume, so the build ties back to the printed top line exactly —</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Export price (USD/t)</t>
+        </is>
+      </c>
+      <c r="B15" s="28">
+        <f>Assumptions!$B$31</f>
+        <v/>
+      </c>
+      <c r="C15" s="28">
+        <f>Assumptions!$C$31</f>
+        <v/>
+      </c>
+      <c r="D15" s="28">
+        <f>Assumptions!$D$31</f>
+        <v/>
+      </c>
+      <c r="E15" s="28">
+        <f>Assumptions!$E$31</f>
+        <v/>
+      </c>
+      <c r="F15" s="28">
+        <f>Assumptions!$F$31</f>
+        <v/>
+      </c>
+      <c r="G15" s="28">
+        <f>Assumptions!$G$31</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>row 12 is the residual and is zero in every historical year. Forecast volume and price compound off</t>
-        </is>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USD/EGP</t>
+        </is>
+      </c>
+      <c r="B16" s="28">
+        <f>Assumptions!$B$32</f>
+        <v/>
+      </c>
+      <c r="C16" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="D16" s="28">
+        <f>Assumptions!$D$32</f>
+        <v/>
+      </c>
+      <c r="E16" s="28">
+        <f>Assumptions!$E$32</f>
+        <v/>
+      </c>
+      <c r="F16" s="28">
+        <f>Assumptions!$F$32</f>
+        <v/>
+      </c>
+      <c r="G16" s="28">
+        <f>Assumptions!$G$32</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>the FY2025 outturn at the growth rates on Assumptions.</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Domestic revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B17" s="29">
+        <f>B12*B14</f>
+        <v/>
+      </c>
+      <c r="C17" s="29">
+        <f>C12*C14</f>
+        <v/>
+      </c>
+      <c r="D17" s="29">
+        <f>D12*D14</f>
+        <v/>
+      </c>
+      <c r="E17" s="29">
+        <f>E12*E14</f>
+        <v/>
+      </c>
+      <c r="F17" s="29">
+        <f>F12*F14</f>
+        <v/>
+      </c>
+      <c r="G17" s="29">
+        <f>G12*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Export revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B18" s="29">
+        <f>B13*B15*B16</f>
+        <v/>
+      </c>
+      <c r="C18" s="29">
+        <f>C13*C15*C16</f>
+        <v/>
+      </c>
+      <c r="D18" s="29">
+        <f>D13*D15*D16</f>
+        <v/>
+      </c>
+      <c r="E18" s="29">
+        <f>E13*E15*E16</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>F13*F15*F16</f>
+        <v/>
+      </c>
+      <c r="G18" s="29">
+        <f>G13*G15*G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REVENUE (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B19" s="30">
+        <f>B17+B18</f>
+        <v/>
+      </c>
+      <c r="C19" s="30">
+        <f>C17+C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="30">
+        <f>D17+D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="30">
+        <f>E17+E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="30">
+        <f>F17+F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="30">
+        <f>G17+G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Blended realised price (EGP/t)</t>
+        </is>
+      </c>
+      <c r="B20" s="29">
+        <f>B19/B10</f>
+        <v/>
+      </c>
+      <c r="C20" s="29">
+        <f>C19/C10</f>
+        <v/>
+      </c>
+      <c r="D20" s="29">
+        <f>D19/D10</f>
+        <v/>
+      </c>
+      <c r="E20" s="29">
+        <f>E19/E10</f>
+        <v/>
+      </c>
+      <c r="F20" s="29">
+        <f>F19/F10</f>
+        <v/>
+      </c>
+      <c r="G20" s="29">
+        <f>G19/G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>COST STACK — EGP PER TONNE OF CEMENT</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Thermal fuel</t>
+        </is>
+      </c>
+      <c r="B23" s="29">
+        <f>Assumptions!$B$16*B9*Assumptions!$B$17*B16</f>
+        <v/>
+      </c>
+      <c r="C23" s="29">
+        <f>Assumptions!$B$16*C9*Assumptions!$B$17*C16</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>Assumptions!$B$16*D9*Assumptions!$B$17*D16</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>Assumptions!$B$16*E9*Assumptions!$B$17*E16</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>Assumptions!$B$16*F9*Assumptions!$B$17*F16</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>Assumptions!$B$16*G9*Assumptions!$B$17*G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Electrical power</t>
+        </is>
+      </c>
+      <c r="B24" s="29">
+        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="C24" s="29">
+        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="D24" s="29">
+        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$D$33</f>
+        <v/>
+      </c>
+      <c r="E24" s="29">
+        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="F24" s="29">
+        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$F$33</f>
+        <v/>
+      </c>
+      <c r="G24" s="29">
+        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$G$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Raw materials &amp; quarrying</t>
+        </is>
+      </c>
+      <c r="B25" s="29">
+        <f>Assumptions!$B$20*Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="C25" s="29">
+        <f>Assumptions!$B$20*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="D25" s="29">
+        <f>Assumptions!$B$20*Assumptions!$D$33</f>
+        <v/>
+      </c>
+      <c r="E25" s="29">
+        <f>Assumptions!$B$20*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="F25" s="29">
+        <f>Assumptions!$B$20*Assumptions!$F$33</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>Assumptions!$B$20*Assumptions!$G$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B26" s="29">
+        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="C26" s="29">
+        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="D26" s="29">
+        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$D$33</f>
+        <v/>
+      </c>
+      <c r="E26" s="29">
+        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="F26" s="29">
+        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$F$33</f>
+        <v/>
+      </c>
+      <c r="G26" s="29">
+        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$G$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Distribution &amp; selling</t>
+        </is>
+      </c>
+      <c r="B27" s="29">
+        <f>Assumptions!$B$23*Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="C27" s="29">
+        <f>Assumptions!$B$23*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="D27" s="29">
+        <f>Assumptions!$B$23*Assumptions!$D$33</f>
+        <v/>
+      </c>
+      <c r="E27" s="29">
+        <f>Assumptions!$B$23*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="F27" s="29">
+        <f>Assumptions!$B$23*Assumptions!$F$33</f>
+        <v/>
+      </c>
+      <c r="G27" s="29">
+        <f>Assumptions!$B$23*Assumptions!$G$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TOTAL VARIABLE (EGP/t)</t>
+        </is>
+      </c>
+      <c r="B28" s="30">
+        <f>SUM(B23:B27)</f>
+        <v/>
+      </c>
+      <c r="C28" s="30">
+        <f>SUM(C23:C27)</f>
+        <v/>
+      </c>
+      <c r="D28" s="30">
+        <f>SUM(D23:D27)</f>
+        <v/>
+      </c>
+      <c r="E28" s="30">
+        <f>SUM(E23:E27)</f>
+        <v/>
+      </c>
+      <c r="F28" s="30">
+        <f>SUM(F23:F27)</f>
+        <v/>
+      </c>
+      <c r="G28" s="30">
+        <f>SUM(G23:G27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>PROFIT AND LOSS — EGP MILLION</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B31" s="9">
+        <f>B19</f>
+        <v/>
+      </c>
+      <c r="C31" s="9">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="D31" s="9">
+        <f>D19</f>
+        <v/>
+      </c>
+      <c r="E31" s="9">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="F31" s="9">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G31" s="9">
+        <f>G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Variable cost</t>
+        </is>
+      </c>
+      <c r="B32" s="29">
+        <f>B28*B10</f>
+        <v/>
+      </c>
+      <c r="C32" s="29">
+        <f>C28*C10</f>
+        <v/>
+      </c>
+      <c r="D32" s="29">
+        <f>D28*D10</f>
+        <v/>
+      </c>
+      <c r="E32" s="29">
+        <f>E28*E10</f>
+        <v/>
+      </c>
+      <c r="F32" s="29">
+        <f>F28*F10</f>
+        <v/>
+      </c>
+      <c r="G32" s="29">
+        <f>G28*G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Fixed cost</t>
+        </is>
+      </c>
+      <c r="B33" s="29">
+        <f>Assumptions!$B$24*B8*Assumptions!$B$9*Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="C33" s="29">
+        <f>Assumptions!$B$24*C8*Assumptions!$B$9*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="D33" s="29">
+        <f>Assumptions!$B$24*D8*Assumptions!$B$9*Assumptions!$D$33</f>
+        <v/>
+      </c>
+      <c r="E33" s="29">
+        <f>Assumptions!$B$24*E8*Assumptions!$B$9*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="F33" s="29">
+        <f>Assumptions!$B$24*F8*Assumptions!$B$9*Assumptions!$F$33</f>
+        <v/>
+      </c>
+      <c r="G33" s="29">
+        <f>Assumptions!$B$24*G8*Assumptions!$B$9*Assumptions!$G$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EBITDA  (AN OUTPUT)</t>
+        </is>
+      </c>
+      <c r="B34" s="30">
+        <f>B31-B32-B33</f>
+        <v/>
+      </c>
+      <c r="C34" s="30">
+        <f>C31-C32-C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="30">
+        <f>D31-D32-D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="30">
+        <f>E31-E32-E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="30">
+        <f>F31-F32-F33</f>
+        <v/>
+      </c>
+      <c r="G34" s="30">
+        <f>G31-G32-G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B35" s="12">
+        <f>B34/B31</f>
+        <v/>
+      </c>
+      <c r="C35" s="12">
+        <f>C34/C31</f>
+        <v/>
+      </c>
+      <c r="D35" s="12">
+        <f>D34/D31</f>
+        <v/>
+      </c>
+      <c r="E35" s="12">
+        <f>E34/E31</f>
+        <v/>
+      </c>
+      <c r="F35" s="12">
+        <f>F34/F31</f>
+        <v/>
+      </c>
+      <c r="G35" s="12">
+        <f>G34/G31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EBITDA per tonne (EGP)</t>
+        </is>
+      </c>
+      <c r="B36" s="29">
+        <f>B34/B10</f>
+        <v/>
+      </c>
+      <c r="C36" s="29">
+        <f>C34/C10</f>
+        <v/>
+      </c>
+      <c r="D36" s="29">
+        <f>D34/D10</f>
+        <v/>
+      </c>
+      <c r="E36" s="29">
+        <f>E34/E10</f>
+        <v/>
+      </c>
+      <c r="F36" s="29">
+        <f>F34/F10</f>
+        <v/>
+      </c>
+      <c r="G36" s="29">
+        <f>G34/G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>VALIDATION — A TEST THAT CAN FAIL</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Bottom-up FY2025 revenue</t>
+        </is>
+      </c>
+      <c r="B39" s="29">
+        <f>B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Disclosed FY2025 revenue</t>
+        </is>
+      </c>
+      <c r="B40" s="9">
+        <f>Assumptions!$B$64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B41" s="12">
+        <f>B39/B40-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Bottom-up FY2025 EBITDA</t>
+        </is>
+      </c>
+      <c r="B42" s="29">
+        <f>B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>EBITDA implied by closing disclosed profit</t>
+        </is>
+      </c>
+      <c r="B43" s="9">
+        <f>'Income Statement'!D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B44" s="12">
+        <f>B42/B43-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Nothing on this sheet is solved to force agreement. Every cost driver is an</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>independent physical or market norm, so a wrong cost stack shows up in rows 41 and 44.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>The model this replaces solved realised price as revenue divided by volume, which</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>made its residual zero for ANY assumption — an identity, not a validation.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A49:J49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5862,7 +6798,7 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>Assumptions!$B$62</f>
+        <f>Assumptions!$B$84</f>
         <v/>
       </c>
     </row>
@@ -5883,8 +6819,8 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="B8" s="30">
-        <f>Assumptions!$B$60</f>
+      <c r="B8" s="31">
+        <f>Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
@@ -6016,8 +6952,8 @@
           <t>Justified price/earnings</t>
         </is>
       </c>
-      <c r="B21" s="30">
-        <f>Assumptions!$B$61</f>
+      <c r="B21" s="31">
+        <f>Assumptions!$B$83</f>
         <v/>
       </c>
     </row>
@@ -6062,7 +6998,7 @@
         </is>
       </c>
       <c r="B26" s="29">
-        <f>Assumptions!$B$8*1000000</f>
+        <f>Assumptions!$B$12*1000000</f>
         <v/>
       </c>
     </row>
@@ -6072,7 +7008,7 @@
           <t>EV per tonne at spot (USD/t)</t>
         </is>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="32">
         <f>B25*1000000/B26/Assumptions!$B$9</f>
         <v/>
       </c>
@@ -6084,7 +7020,7 @@
         </is>
       </c>
       <c r="B28" s="29">
-        <f>Assumptions!$B$58</f>
+        <f>Assumptions!$B$80</f>
         <v/>
       </c>
     </row>
@@ -6106,7 +7042,7 @@
         </is>
       </c>
       <c r="B30" s="29">
-        <f>Assumptions!$B$59</f>
+        <f>Assumptions!$B$81</f>
         <v/>
       </c>
     </row>
@@ -6291,23 +7227,23 @@
         </is>
       </c>
       <c r="B5" s="9">
-        <f>'Unit Build'!E10</f>
+        <f>'Unit Build'!C31</f>
         <v/>
       </c>
       <c r="C5" s="9">
-        <f>'Unit Build'!F10</f>
+        <f>'Unit Build'!D31</f>
         <v/>
       </c>
       <c r="D5" s="9">
-        <f>'Unit Build'!G10</f>
+        <f>'Unit Build'!E31</f>
         <v/>
       </c>
       <c r="E5" s="9">
-        <f>'Unit Build'!H10</f>
+        <f>'Unit Build'!F31</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>'Unit Build'!I10</f>
+        <f>'Unit Build'!G31</f>
         <v/>
       </c>
     </row>
@@ -6317,24 +7253,24 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B6" s="11">
-        <f>Assumptions!$B$35</f>
-        <v/>
-      </c>
-      <c r="C6" s="11">
-        <f>Assumptions!$C$35</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
-        <f>Assumptions!$D$35</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
-        <f>Assumptions!$E$35</f>
-        <v/>
-      </c>
-      <c r="F6" s="11">
-        <f>Assumptions!$F$35</f>
+      <c r="B6" s="12">
+        <f>B7/B5</f>
+        <v/>
+      </c>
+      <c r="C6" s="12">
+        <f>C7/C5</f>
+        <v/>
+      </c>
+      <c r="D6" s="12">
+        <f>D7/D5</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>E7/E5</f>
+        <v/>
+      </c>
+      <c r="F6" s="12">
+        <f>F7/F5</f>
         <v/>
       </c>
     </row>
@@ -6344,24 +7280,24 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="29">
-        <f>B5*B6</f>
-        <v/>
-      </c>
-      <c r="C7" s="29">
-        <f>C5*C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="29">
-        <f>D5*D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="29">
-        <f>E5*E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="29">
-        <f>F5*F6</f>
+      <c r="B7" s="9">
+        <f>'Unit Build'!C34</f>
+        <v/>
+      </c>
+      <c r="C7" s="9">
+        <f>'Unit Build'!D34</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>'Unit Build'!E34</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
+        <f>'Unit Build'!F34</f>
+        <v/>
+      </c>
+      <c r="F7" s="9">
+        <f>'Unit Build'!G34</f>
         <v/>
       </c>
     </row>
@@ -6476,81 +7412,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>+ Depreciation &amp; amortisation</t>
+          <t>Memo: capital expenditure</t>
         </is>
       </c>
       <c r="B12" s="29">
-        <f>B8</f>
+        <f>B5*Assumptions!$B$37</f>
         <v/>
       </c>
       <c r="C12" s="29">
-        <f>C8</f>
+        <f>C5*Assumptions!$C$37</f>
         <v/>
       </c>
       <c r="D12" s="29">
-        <f>D8</f>
+        <f>D5*Assumptions!$D$37</f>
         <v/>
       </c>
       <c r="E12" s="29">
-        <f>E8</f>
+        <f>E5*Assumptions!$E$37</f>
         <v/>
       </c>
       <c r="F12" s="29">
-        <f>F8</f>
+        <f>F5*Assumptions!$F$37</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>− Capital expenditure</t>
+          <t>Memo: change in working capital</t>
         </is>
       </c>
       <c r="B13" s="29">
-        <f>B5*Assumptions!$B$37</f>
+        <f>(B5-'Unit Build'!B31)*Assumptions!$B$40</f>
         <v/>
       </c>
       <c r="C13" s="29">
-        <f>C5*Assumptions!$C$37</f>
+        <f>(C5-B5)*Assumptions!$B$40</f>
         <v/>
       </c>
       <c r="D13" s="29">
-        <f>D5*Assumptions!$D$37</f>
+        <f>(D5-C5)*Assumptions!$B$40</f>
         <v/>
       </c>
       <c r="E13" s="29">
-        <f>E5*Assumptions!$E$37</f>
+        <f>(E5-D5)*Assumptions!$B$40</f>
         <v/>
       </c>
       <c r="F13" s="29">
-        <f>F5*Assumptions!$F$37</f>
+        <f>(F5-E5)*Assumptions!$B$40</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>− Change in working capital</t>
+          <t>Net reinvestment  (growth ÷ terminal ROIC)</t>
         </is>
       </c>
       <c r="B14" s="29">
-        <f>(B5-'Unit Build'!D10)*Assumptions!$B$41</f>
+        <f>MAX(B11-$B$23,0)/$B$24</f>
         <v/>
       </c>
       <c r="C14" s="29">
-        <f>(C5-B5)*Assumptions!$B$41</f>
+        <f>MAX(C11-B11,0)/$B$24</f>
         <v/>
       </c>
       <c r="D14" s="29">
-        <f>(D5-C5)*Assumptions!$B$41</f>
+        <f>MAX(D11-C11,0)/$B$24</f>
         <v/>
       </c>
       <c r="E14" s="29">
-        <f>(E5-D5)*Assumptions!$B$41</f>
+        <f>MAX(E11-D11,0)/$B$24</f>
         <v/>
       </c>
       <c r="F14" s="29">
-        <f>(F5-E5)*Assumptions!$B$41</f>
+        <f>MAX(F11-E11,0)/$B$24</f>
         <v/>
       </c>
     </row>
@@ -6560,24 +7496,24 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B15" s="32">
-        <f>B11+B12-B13-B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="32">
-        <f>C11+C12-C13-C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="32">
-        <f>D11+D12-D13-D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="32">
-        <f>E11+E12-E13-E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="32">
-        <f>F11+F12-F13-F14</f>
+      <c r="B15" s="30">
+        <f>(B11-B14)*(1-Assumptions!$B$56)</f>
+        <v/>
+      </c>
+      <c r="C15" s="30">
+        <f>C11-C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="30">
+        <f>D11-D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="30">
+        <f>E11-E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="30">
+        <f>F11-F14</f>
         <v/>
       </c>
     </row>
@@ -6642,23 +7578,23 @@
         </is>
       </c>
       <c r="B18" s="33">
-        <f>1/(1+B17)</f>
+        <f>1/(1+B17)^((1-Assumptions!$B$56)/2)</f>
         <v/>
       </c>
       <c r="C18" s="33">
-        <f>B18/(1+C17)</f>
+        <f>1/(1+B17)^(1-Assumptions!$B$56+0.5)</f>
         <v/>
       </c>
       <c r="D18" s="33">
-        <f>C18/(1+D17)</f>
+        <f>1/((1+B17)*(1+C17)^(1-Assumptions!$B$56+0.5))</f>
         <v/>
       </c>
       <c r="E18" s="33">
-        <f>D18/(1+E17)</f>
+        <f>1/((1+B17)*(1+C17)*(1+D17)^(1-Assumptions!$B$56+0.5))</f>
         <v/>
       </c>
       <c r="F18" s="33">
-        <f>E18/(1+F17)</f>
+        <f>1/((1+B17)*(1+C17)*(1+D17)*(1+E17)^(1-Assumptions!$B$56+0.5))</f>
         <v/>
       </c>
     </row>
@@ -6710,18 +7646,18 @@
         </is>
       </c>
       <c r="B22" s="29">
-        <f>Assumptions!$B$8*1000000*Assumptions!$B$58*Assumptions!$B$9/1000000</f>
+        <f>Assumptions!$B$12*1000000*Assumptions!$B$80*Assumptions!$B$9/1000000</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Terminal NOPAT  (year-5 NOPAT × (1+g))</t>
+          <t>FY2025 NOPAT (the reinvestment base)</t>
         </is>
       </c>
       <c r="B23" s="29">
-        <f>F11*(1+Assumptions!$B$24)</f>
+        <f>('Income Statement'!D6-'Income Statement'!D8)*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
     </row>
@@ -6732,7 +7668,7 @@
         </is>
       </c>
       <c r="B24" s="12">
-        <f>B23/B22</f>
+        <f>F11*(1+Assumptions!$B$55)/B22</f>
         <v/>
       </c>
     </row>
@@ -6743,7 +7679,7 @@
         </is>
       </c>
       <c r="B25" s="12">
-        <f>Assumptions!$B$24/B24</f>
+        <f>Assumptions!$B$55/B24</f>
         <v/>
       </c>
     </row>
@@ -6754,7 +7690,7 @@
         </is>
       </c>
       <c r="B26" s="29">
-        <f>B23*(1-B25)/($C$53-Assumptions!$B$24)</f>
+        <f>B28*(1-B25)/($C$53-Assumptions!$B$55)</f>
         <v/>
       </c>
     </row>
@@ -6766,6 +7702,17 @@
       </c>
       <c r="B27" s="29">
         <f>B26*F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Terminal NOPAT</t>
+        </is>
+      </c>
+      <c r="B28" s="29">
+        <f>F11*(1+Assumptions!$B$55)</f>
         <v/>
       </c>
     </row>
@@ -6811,7 +7758,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="30">
         <f>B30+B31</f>
         <v/>
       </c>
@@ -6830,7 +7777,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cash and equivalents</t>
+          <t>Cash at the valuation date</t>
         </is>
       </c>
       <c r="B34" s="29">
@@ -6845,7 +7792,7 @@
         </is>
       </c>
       <c r="B35" s="29">
-        <f>-Assumptions!$B$17</f>
+        <f>-Assumptions!$B$50</f>
         <v/>
       </c>
     </row>
@@ -6866,8 +7813,8 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B37" s="32">
-        <f>B32+B36</f>
+      <c r="B37" s="30">
+        <f>B32+B36-B40</f>
         <v/>
       </c>
     </row>
@@ -6877,7 +7824,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="35">
         <f>Assumptions!$B$6</f>
         <v/>
       </c>
@@ -6890,6 +7837,17 @@
       </c>
       <c r="B39" s="13">
         <f>B37/B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Less non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B40" s="29">
+        <f>Assumptions!$B$61</f>
         <v/>
       </c>
     </row>
@@ -6914,7 +7872,7 @@
         </is>
       </c>
       <c r="C42" s="34">
-        <f>Assumptions!$B$12</f>
+        <f>Assumptions!$B$45</f>
         <v/>
       </c>
     </row>
@@ -6925,7 +7883,7 @@
         </is>
       </c>
       <c r="C43" s="34">
-        <f>-Assumptions!$B$13</f>
+        <f>-Assumptions!$B$46</f>
         <v/>
       </c>
     </row>
@@ -6947,7 +7905,7 @@
         </is>
       </c>
       <c r="C45" s="34">
-        <f>C44+Assumptions!$B$15*Assumptions!$B$14</f>
+        <f>C44+Assumptions!$B$48*Assumptions!$B$47</f>
         <v/>
       </c>
     </row>
@@ -6957,7 +7915,7 @@
           <t>WACC — explicit window</t>
         </is>
       </c>
-      <c r="C46" s="35">
+      <c r="C46" s="36">
         <f>(1-C49)*C45+C49*C48</f>
         <v/>
       </c>
@@ -6969,7 +7927,7 @@
         </is>
       </c>
       <c r="C48" s="34">
-        <f>Assumptions!$B$16*(1-Assumptions!$B$7)</f>
+        <f>Assumptions!$B$49*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
     </row>
@@ -6979,8 +7937,8 @@
           <t>Debt weight  D/(D+E)</t>
         </is>
       </c>
-      <c r="C49" s="36">
-        <f>Assumptions!$B$17/(Assumptions!$B$17+C50)</f>
+      <c r="C49" s="37">
+        <f>Assumptions!$B$50/(Assumptions!$B$50+C50)</f>
         <v/>
       </c>
     </row>
@@ -6998,11 +7956,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Terminal cost of equity  (rf_term + β × ERP_term)</t>
+          <t>Terminal cost of equity  (rf_term + β_L × ERP_term)</t>
         </is>
       </c>
       <c r="C51" s="34">
-        <f>Assumptions!$B$20+Assumptions!$B$15*Assumptions!$B$21</f>
+        <f>Assumptions!$B$51+C56*Assumptions!$B$52</f>
         <v/>
       </c>
     </row>
@@ -7013,7 +7971,7 @@
         </is>
       </c>
       <c r="C52" s="34">
-        <f>Assumptions!$B$22*(1-Assumptions!$B$7)</f>
+        <f>Assumptions!$B$53*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
     </row>
@@ -7023,8 +7981,8 @@
           <t>WACC — terminal</t>
         </is>
       </c>
-      <c r="C53" s="35">
-        <f>(1-Assumptions!$B$23)*C51+Assumptions!$B$23*C52</f>
+      <c r="C53" s="36">
+        <f>(1-Assumptions!$B$54)*C51+Assumptions!$B$54*C52</f>
         <v/>
       </c>
     </row>
@@ -7035,7 +7993,7 @@
         </is>
       </c>
       <c r="C54" s="34">
-        <f>Assumptions!$B$12+Assumptions!$B$15*Assumptions!$B$14</f>
+        <f>Assumptions!$B$45+Assumptions!$B$48*Assumptions!$B$47</f>
         <v/>
       </c>
     </row>
@@ -7047,6 +8005,17 @@
       </c>
       <c r="C55" s="29">
         <f>(C54-C45)*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Terminal beta, RE-LEVERED to the terminal structure (Hamada)</t>
+        </is>
+      </c>
+      <c r="C56" s="27">
+        <f>Assumptions!$B$48*(1+(1-Assumptions!$B$7)*Assumptions!$B$54/(1-Assumptions!$B$54))</f>
         <v/>
       </c>
     </row>
@@ -7308,15 +8277,15 @@
         </is>
       </c>
       <c r="B8" s="29">
-        <f>B5*0.094</f>
+        <f>B5*Assumptions!$B$75</f>
         <v/>
       </c>
       <c r="C8" s="29">
-        <f>C5*0.062</f>
+        <f>C5*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D8" s="29">
-        <f>D5*0.046</f>
+        <f>D5*Assumptions!$B$77</f>
         <v/>
       </c>
       <c r="E8" s="9">
@@ -7351,11 +8320,11 @@
         <v/>
       </c>
       <c r="C9" s="29">
-        <f>Assumptions!$B$49-C8</f>
+        <f>Assumptions!$B$68-C8</f>
         <v/>
       </c>
       <c r="D9" s="29">
-        <f>D14/(1-Assumptions!$B$7)-D10</f>
+        <f>D14/(1-Assumptions!$B$8)-D10</f>
         <v/>
       </c>
       <c r="E9" s="29">
@@ -7386,15 +8355,15 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>Assumptions!$B$52</f>
+        <f>Assumptions!$B$71</f>
         <v/>
       </c>
       <c r="C10" s="29">
-        <f>(C14-C11)/(1-Assumptions!$B$7)-C9</f>
+        <f>Assumptions!$B$59/1.25*0.9*Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="D10" s="29">
-        <f>C10</f>
+        <f>(Assumptions!$B$59+Assumptions!$B$59/1.25)/2*Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="E10" s="29">
@@ -7429,7 +8398,7 @@
         <v/>
       </c>
       <c r="C11" s="29">
-        <f>Assumptions!$B$53*Assumptions!$B$54-Assumptions!$B$55</f>
+        <f>Assumptions!$B$92*Assumptions!$B$93-Assumptions!$B$94</f>
         <v/>
       </c>
       <c r="D11" s="29">
@@ -7542,34 +8511,34 @@
         </is>
       </c>
       <c r="B14" s="26">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$B$65</f>
         <v/>
       </c>
       <c r="C14" s="26">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$B$66</f>
         <v/>
       </c>
       <c r="D14" s="26">
-        <f>Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="E14" s="32">
+        <f>Assumptions!$B$67</f>
+        <v/>
+      </c>
+      <c r="E14" s="30">
         <f>E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="30">
         <f>F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="30">
         <f>G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <f>H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="30">
         <f>I12-I13</f>
         <v/>
       </c>
@@ -7581,15 +8550,15 @@
         </is>
       </c>
       <c r="B15" s="9">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$B$65</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$B$66</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>Assumptions!$C$48</f>
+        <f>Assumptions!$B$67</f>
         <v/>
       </c>
     </row>
@@ -7600,15 +8569,15 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>B14/Assumptions!$B$6</f>
+        <f>B14/Assumptions!$B$72</f>
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>C14/Assumptions!$B$6</f>
+        <f>C14/Assumptions!$B$73</f>
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>D14/Assumptions!$B$6</f>
+        <f>D14/Assumptions!$B$74</f>
         <v/>
       </c>
       <c r="E16" s="15">

--- a/engine/scem_study/SCEM_Valuation_Model_06082026_public.xlsx
+++ b/engine/scem_study/SCEM_Valuation_Model_06082026_public.xlsx
@@ -25,7 +25,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer &amp; Sector" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" calcCompleted="0"/>
 </workbook>
 </file>
 
@@ -36,8 +36,8 @@
     <numFmt numFmtId="165" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="169" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="170" formatCode="0.00x"/>
     <numFmt numFmtId="171" formatCode="0.0000"/>
     <numFmt numFmtId="172" formatCode="0.000%"/>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,7 +131,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,11 +148,12 @@
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -952,35 +953,35 @@
           <t>Property, plant and equipment (net)</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="23" t="n">
         <v>2285.624</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>Assumptions!$B$69-C6-C7</f>
         <v/>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>C5</f>
         <v/>
       </c>
-      <c r="E5" s="29">
-        <f>D5+DCF!B13-DCF!B8</f>
-        <v/>
-      </c>
-      <c r="F5" s="29">
-        <f>E5+DCF!C13-DCF!C8</f>
-        <v/>
-      </c>
-      <c r="G5" s="29">
-        <f>F5+DCF!D13-DCF!D8</f>
-        <v/>
-      </c>
-      <c r="H5" s="29">
-        <f>G5+DCF!E13-DCF!E8</f>
-        <v/>
-      </c>
-      <c r="I5" s="29">
-        <f>H5+DCF!F13-DCF!F8</f>
+      <c r="E5" s="30">
+        <f>D5+DCF!B12-DCF!B8</f>
+        <v/>
+      </c>
+      <c r="F5" s="30">
+        <f>E5+DCF!C12-DCF!C8</f>
+        <v/>
+      </c>
+      <c r="G5" s="30">
+        <f>F5+DCF!D12-DCF!D8</f>
+        <v/>
+      </c>
+      <c r="H5" s="30">
+        <f>G5+DCF!E12-DCF!E8</f>
+        <v/>
+      </c>
+      <c r="I5" s="30">
+        <f>H5+DCF!F12-DCF!F8</f>
         <v/>
       </c>
     </row>
@@ -990,34 +991,34 @@
           <t>Working capital (net)</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>850</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>900</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>C6</f>
         <v/>
       </c>
-      <c r="E6" s="29">
-        <f>D6+DCF!B14</f>
-        <v/>
-      </c>
-      <c r="F6" s="29">
-        <f>E6+DCF!C14</f>
-        <v/>
-      </c>
-      <c r="G6" s="29">
-        <f>F6+DCF!D14</f>
-        <v/>
-      </c>
-      <c r="H6" s="29">
-        <f>G6+DCF!E14</f>
-        <v/>
-      </c>
-      <c r="I6" s="29">
-        <f>H6+DCF!F14</f>
+      <c r="E6" s="30">
+        <f>D6+DCF!B13</f>
+        <v/>
+      </c>
+      <c r="F6" s="30">
+        <f>E6+DCF!C13</f>
+        <v/>
+      </c>
+      <c r="G6" s="30">
+        <f>F6+DCF!D13</f>
+        <v/>
+      </c>
+      <c r="H6" s="30">
+        <f>G6+DCF!E13</f>
+        <v/>
+      </c>
+      <c r="I6" s="30">
+        <f>H6+DCF!F13</f>
         <v/>
       </c>
     </row>
@@ -1027,35 +1028,35 @@
           <t>Cash and equivalents</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>1078</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>Assumptions!$B$59/1.25</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>Assumptions!$B$59+DCF!B15*Assumptions!$B$56/(1-Assumptions!$B$56)</f>
-        <v/>
-      </c>
-      <c r="E7" s="29">
-        <f>D7+'Cash Flow'!E16</f>
-        <v/>
-      </c>
-      <c r="F7" s="29">
-        <f>E7+'Cash Flow'!F16</f>
-        <v/>
-      </c>
-      <c r="G7" s="29">
-        <f>F7+'Cash Flow'!G16</f>
-        <v/>
-      </c>
-      <c r="H7" s="29">
-        <f>G7+'Cash Flow'!H16</f>
-        <v/>
-      </c>
-      <c r="I7" s="29">
-        <f>H7+'Cash Flow'!I16</f>
+        <f>Assumptions!$B$59</f>
+        <v/>
+      </c>
+      <c r="E7" s="30">
+        <f>D7+'Cash Flow'!E14</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
+        <f>E7+'Cash Flow'!F14</f>
+        <v/>
+      </c>
+      <c r="G7" s="30">
+        <f>F7+'Cash Flow'!G14</f>
+        <v/>
+      </c>
+      <c r="H7" s="30">
+        <f>G7+'Cash Flow'!H14</f>
+        <v/>
+      </c>
+      <c r="I7" s="30">
+        <f>H7+'Cash Flow'!I14</f>
         <v/>
       </c>
     </row>
@@ -1065,7 +1066,7 @@
           <t>Total assets (condensed)</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
@@ -1073,27 +1074,27 @@
         <f>Assumptions!$B$69</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -1104,35 +1105,35 @@
           <t>Gross debt</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="33">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="33">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="33">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
@@ -1143,35 +1144,35 @@
           <t>Other liabilities</t>
         </is>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <f>B11-B9</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>C11-C9</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>D11-D9</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>E11-E9</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>F11-F9</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>G11-G9</f>
         <v/>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <f>H11-H9</f>
         <v/>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="30">
         <f>I11-I9</f>
         <v/>
       </c>
@@ -1182,7 +1183,7 @@
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>B8-B12</f>
         <v/>
       </c>
@@ -1190,27 +1191,27 @@
         <f>Assumptions!$B$70</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>D8-D12</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>E8-E12</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>F8-F12</f>
         <v/>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>G8-G12</f>
         <v/>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="30">
         <f>H8-H12</f>
         <v/>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="30">
         <f>I8-I12</f>
         <v/>
       </c>
@@ -1221,11 +1222,11 @@
           <t>Shareholders' equity</t>
         </is>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>C12-Assumptions!$B$66</f>
         <v/>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>C8-C11</f>
         <v/>
       </c>
@@ -1233,24 +1234,24 @@
         <f>Assumptions!$B$60</f>
         <v/>
       </c>
-      <c r="E12" s="30">
-        <f>D12+'Income Statement'!E14-'Cash Flow'!E15</f>
-        <v/>
-      </c>
-      <c r="F12" s="30">
-        <f>E12+'Income Statement'!F14-'Cash Flow'!F15</f>
-        <v/>
-      </c>
-      <c r="G12" s="30">
-        <f>F12+'Income Statement'!G14-'Cash Flow'!G15</f>
-        <v/>
-      </c>
-      <c r="H12" s="30">
-        <f>G12+'Income Statement'!H14-'Cash Flow'!H15</f>
-        <v/>
-      </c>
-      <c r="I12" s="30">
-        <f>H12+'Income Statement'!I14-'Cash Flow'!I15</f>
+      <c r="E12" s="31">
+        <f>D12+'Income Statement'!E14-'Cash Flow'!E13</f>
+        <v/>
+      </c>
+      <c r="F12" s="31">
+        <f>E12+'Income Statement'!F14-'Cash Flow'!F13</f>
+        <v/>
+      </c>
+      <c r="G12" s="31">
+        <f>F12+'Income Statement'!G14-'Cash Flow'!G13</f>
+        <v/>
+      </c>
+      <c r="H12" s="31">
+        <f>G12+'Income Statement'!H14-'Cash Flow'!H13</f>
+        <v/>
+      </c>
+      <c r="I12" s="31">
+        <f>H12+'Income Statement'!I14-'Cash Flow'!I13</f>
         <v/>
       </c>
     </row>
@@ -1260,7 +1261,7 @@
           <t>Equity — reported cross-check</t>
         </is>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>C12+Assumptions!$B$67</f>
         <v/>
       </c>
@@ -1271,35 +1272,35 @@
           <t>Net cash</t>
         </is>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <f>B7-B9</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>C7-C9</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>D7-D9</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>E7-E9</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>F7-F9</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <f>G7-G9</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <f>H7-H9</f>
         <v/>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="30">
         <f>I7-I9</f>
         <v/>
       </c>
@@ -1427,28 +1428,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -1484,54 +1485,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>− Change in working capital</t>
-        </is>
-      </c>
-      <c r="E6" s="29">
-        <f>-DCF!B14</f>
-        <v/>
-      </c>
-      <c r="F6" s="29">
-        <f>-DCF!C14</f>
-        <v/>
-      </c>
-      <c r="G6" s="29">
-        <f>-DCF!D14</f>
-        <v/>
-      </c>
-      <c r="H6" s="29">
-        <f>-DCF!E14</f>
-        <v/>
-      </c>
-      <c r="I6" s="29">
-        <f>-DCF!F14</f>
+          <t>Less change in working capital</t>
+        </is>
+      </c>
+      <c r="E6" s="30">
+        <f>-DCF!B13</f>
+        <v/>
+      </c>
+      <c r="F6" s="30">
+        <f>-DCF!C13</f>
+        <v/>
+      </c>
+      <c r="G6" s="30">
+        <f>-DCF!D13</f>
+        <v/>
+      </c>
+      <c r="H6" s="30">
+        <f>-DCF!E13</f>
+        <v/>
+      </c>
+      <c r="I6" s="30">
+        <f>-DCF!F13</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>− Capital expenditure</t>
-        </is>
-      </c>
-      <c r="E7" s="29">
-        <f>-DCF!B13</f>
-        <v/>
-      </c>
-      <c r="F7" s="29">
-        <f>-DCF!C13</f>
-        <v/>
-      </c>
-      <c r="G7" s="29">
-        <f>-DCF!D13</f>
-        <v/>
-      </c>
-      <c r="H7" s="29">
-        <f>-DCF!E13</f>
-        <v/>
-      </c>
-      <c r="I7" s="29">
-        <f>-DCF!F13</f>
+          <t>Less capital expenditure</t>
+        </is>
+      </c>
+      <c r="E7" s="30">
+        <f>-DCF!B12</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
+        <f>-DCF!C12</f>
+        <v/>
+      </c>
+      <c r="G7" s="30">
+        <f>-DCF!D12</f>
+        <v/>
+      </c>
+      <c r="H7" s="30">
+        <f>-DCF!E12</f>
+        <v/>
+      </c>
+      <c r="I7" s="30">
+        <f>-DCF!F12</f>
         <v/>
       </c>
     </row>
@@ -1541,23 +1542,23 @@
           <t>Operating free cash flow</t>
         </is>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -1592,189 +1593,135 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>+ D&amp;A</t>
-        </is>
-      </c>
-      <c r="E10" s="9">
-        <f>DCF!B12</f>
-        <v/>
-      </c>
-      <c r="F10" s="9">
-        <f>DCF!C12</f>
-        <v/>
-      </c>
-      <c r="G10" s="9">
-        <f>DCF!D12</f>
-        <v/>
-      </c>
-      <c r="H10" s="9">
-        <f>DCF!E12</f>
-        <v/>
-      </c>
-      <c r="I10" s="9">
-        <f>DCF!F12</f>
+          <t>Less net reinvestment (growth at terminal ROIC)</t>
+        </is>
+      </c>
+      <c r="E10" s="30">
+        <f>-DCF!B14</f>
+        <v/>
+      </c>
+      <c r="F10" s="30">
+        <f>-DCF!C14</f>
+        <v/>
+      </c>
+      <c r="G10" s="30">
+        <f>-DCF!D14</f>
+        <v/>
+      </c>
+      <c r="H10" s="30">
+        <f>-DCF!E14</f>
+        <v/>
+      </c>
+      <c r="I10" s="30">
+        <f>-DCF!F14</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>− Capex</t>
-        </is>
-      </c>
-      <c r="E11" s="29">
-        <f>-DCF!B13</f>
-        <v/>
-      </c>
-      <c r="F11" s="29">
-        <f>-DCF!C13</f>
-        <v/>
-      </c>
-      <c r="G11" s="29">
-        <f>-DCF!D13</f>
-        <v/>
-      </c>
-      <c r="H11" s="29">
-        <f>-DCF!E13</f>
-        <v/>
-      </c>
-      <c r="I11" s="29">
-        <f>-DCF!F13</f>
+          <t>Free cash flow to the firm</t>
+        </is>
+      </c>
+      <c r="E11" s="31">
+        <f>DCF!B15</f>
+        <v/>
+      </c>
+      <c r="F11" s="31">
+        <f>DCF!C15</f>
+        <v/>
+      </c>
+      <c r="G11" s="31">
+        <f>DCF!D15</f>
+        <v/>
+      </c>
+      <c r="H11" s="31">
+        <f>DCF!E15</f>
+        <v/>
+      </c>
+      <c r="I11" s="31">
+        <f>DCF!F15</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>− Change in working capital</t>
-        </is>
-      </c>
-      <c r="E12" s="29">
-        <f>-DCF!B14</f>
-        <v/>
-      </c>
-      <c r="F12" s="29">
-        <f>-DCF!C14</f>
-        <v/>
-      </c>
-      <c r="G12" s="29">
-        <f>-DCF!D14</f>
-        <v/>
-      </c>
-      <c r="H12" s="29">
-        <f>-DCF!E14</f>
-        <v/>
-      </c>
-      <c r="I12" s="29">
-        <f>-DCF!F14</f>
+          <t>Treasury income after tax</t>
+        </is>
+      </c>
+      <c r="E12" s="30">
+        <f>'Income Statement'!E10*(1-Assumptions!$B$7)</f>
+        <v/>
+      </c>
+      <c r="F12" s="30">
+        <f>'Income Statement'!F10*(1-Assumptions!$B$7)</f>
+        <v/>
+      </c>
+      <c r="G12" s="30">
+        <f>'Income Statement'!G10*(1-Assumptions!$B$7)</f>
+        <v/>
+      </c>
+      <c r="H12" s="30">
+        <f>'Income Statement'!H10*(1-Assumptions!$B$7)</f>
+        <v/>
+      </c>
+      <c r="I12" s="30">
+        <f>'Income Statement'!I10*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Free cash flow to the firm</t>
+          <t>Dividends paid</t>
         </is>
       </c>
       <c r="E13" s="30">
-        <f>SUM(E9:E12)</f>
+        <f>'Income Statement'!E14*Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="F13" s="30">
-        <f>SUM(F9:F12)</f>
+        <f>'Income Statement'!F14*Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>SUM(G9:G12)</f>
+        <f>'Income Statement'!G14*Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="H13" s="30">
-        <f>SUM(H9:H12)</f>
+        <f>'Income Statement'!H14*Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="I13" s="30">
-        <f>SUM(I9:I12)</f>
+        <f>'Income Statement'!I14*Assumptions!$B$41</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Treasury income after tax</t>
-        </is>
-      </c>
-      <c r="E14" s="29">
-        <f>'Income Statement'!E10*(1-Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="F14" s="29">
-        <f>'Income Statement'!F10*(1-Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="G14" s="29">
-        <f>'Income Statement'!G10*(1-Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="H14" s="29">
-        <f>'Income Statement'!H10*(1-Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="I14" s="29">
-        <f>'Income Statement'!I10*(1-Assumptions!$B$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Dividends paid</t>
-        </is>
-      </c>
-      <c r="E15" s="29">
-        <f>'Income Statement'!E14*Assumptions!$B$41</f>
-        <v/>
-      </c>
-      <c r="F15" s="29">
-        <f>'Income Statement'!F14*Assumptions!$B$41</f>
-        <v/>
-      </c>
-      <c r="G15" s="29">
-        <f>'Income Statement'!G14*Assumptions!$B$41</f>
-        <v/>
-      </c>
-      <c r="H15" s="29">
-        <f>'Income Statement'!H14*Assumptions!$B$41</f>
-        <v/>
-      </c>
-      <c r="I15" s="29">
-        <f>'Income Statement'!I14*Assumptions!$B$41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="E16" s="30">
-        <f>'Income Statement'!E14+DCF!B12-DCF!B13-DCF!B14-E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="30">
-        <f>'Income Statement'!F14+DCF!C12-DCF!C13-DCF!C14-F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="30">
-        <f>'Income Statement'!G14+DCF!D12-DCF!D13-DCF!D14-G15</f>
-        <v/>
-      </c>
-      <c r="H16" s="30">
-        <f>'Income Statement'!H14+DCF!E12-DCF!E13-DCF!E14-H15</f>
-        <v/>
-      </c>
-      <c r="I16" s="30">
-        <f>'Income Statement'!I14+DCF!F12-DCF!F13-DCF!F14-I15</f>
+      <c r="E14" s="31">
+        <f>'Income Statement'!E14+DCF!B8-DCF!B12-DCF!B13-E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="31">
+        <f>'Income Statement'!F14+DCF!C8-DCF!C12-DCF!C13-F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="31">
+        <f>'Income Statement'!G14+DCF!D8-DCF!D12-DCF!D13-G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="31">
+        <f>'Income Statement'!H14+DCF!E8-DCF!E12-DCF!E13-H13</f>
+        <v/>
+      </c>
+      <c r="I14" s="31">
+        <f>'Income Statement'!I14+DCF!F8-DCF!F12-DCF!F13-I13</f>
         <v/>
       </c>
     </row>
@@ -2058,36 +2005,28 @@
           <t>Sales volume (Mt)</t>
         </is>
       </c>
-      <c r="B9" s="8">
+      <c r="D9" s="28">
         <f>'Unit Build'!B10</f>
         <v/>
       </c>
-      <c r="C9" s="8">
+      <c r="E9" s="28">
         <f>'Unit Build'!C10</f>
         <v/>
       </c>
-      <c r="D9" s="8">
+      <c r="F9" s="28">
         <f>'Unit Build'!D10</f>
         <v/>
       </c>
-      <c r="E9" s="8">
+      <c r="G9" s="28">
         <f>'Unit Build'!E10</f>
         <v/>
       </c>
-      <c r="F9" s="8">
+      <c r="H9" s="28">
         <f>'Unit Build'!F10</f>
         <v/>
       </c>
-      <c r="G9" s="8">
+      <c r="I9" s="28">
         <f>'Unit Build'!G10</f>
-        <v/>
-      </c>
-      <c r="H9" s="8">
-        <f>'Unit Build'!H10</f>
-        <v/>
-      </c>
-      <c r="I9" s="8">
-        <f>'Unit Build'!I10</f>
         <v/>
       </c>
     </row>
@@ -2097,75 +2036,59 @@
           <t>Realised price (EGP/t)</t>
         </is>
       </c>
-      <c r="B10" s="9">
+      <c r="D10" s="9">
         <f>'Unit Build'!B20</f>
         <v/>
       </c>
-      <c r="C10" s="9">
+      <c r="E10" s="9">
         <f>'Unit Build'!C20</f>
         <v/>
       </c>
-      <c r="D10" s="9">
+      <c r="F10" s="9">
         <f>'Unit Build'!D20</f>
         <v/>
       </c>
-      <c r="E10" s="9">
+      <c r="G10" s="9">
         <f>'Unit Build'!E20</f>
         <v/>
       </c>
-      <c r="F10" s="9">
+      <c r="H10" s="9">
         <f>'Unit Build'!F20</f>
         <v/>
       </c>
-      <c r="G10" s="9">
+      <c r="I10" s="9">
         <f>'Unit Build'!G20</f>
-        <v/>
-      </c>
-      <c r="H10" s="9">
-        <f>'Unit Build'!H20</f>
-        <v/>
-      </c>
-      <c r="I10" s="9">
-        <f>'Unit Build'!I20</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Capacity utilisation</t>
-        </is>
-      </c>
-      <c r="B11" s="11">
+          <t>Kiln utilisation</t>
+        </is>
+      </c>
+      <c r="D11" s="11">
         <f>'Unit Build'!B6</f>
         <v/>
       </c>
-      <c r="C11" s="11">
+      <c r="E11" s="11">
         <f>'Unit Build'!C6</f>
         <v/>
       </c>
-      <c r="D11" s="11">
+      <c r="F11" s="11">
         <f>'Unit Build'!D6</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="G11" s="11">
         <f>'Unit Build'!E6</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="H11" s="11">
         <f>'Unit Build'!F6</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="I11" s="11">
         <f>'Unit Build'!G6</f>
-        <v/>
-      </c>
-      <c r="H11" s="11">
-        <f>'Unit Build'!H6</f>
-        <v/>
-      </c>
-      <c r="I11" s="11">
-        <f>'Unit Build'!I6</f>
         <v/>
       </c>
     </row>
@@ -2336,10 +2259,10 @@
           <t>1M (1 month)</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
@@ -2366,10 +2289,10 @@
           <t>3M (3 months)</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>62</v>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
@@ -2477,84 +2400,84 @@
       <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Market panel verdict (Egypt)</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>PASS — skill +0.0158, 90% interval [0.009, 0.022]</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>This name's verdict</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>PARITY at every bootstrap block size {2,3,4}</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>This name's CRPS skill vs a random walk</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>-0.1276 — BELOW zero</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Coverage 50 / 80 / 90</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>0.76 / 0.82 / 0.94 against nominal 0.50 / 0.80 / 0.90 — OVER-COVERED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Cone width versus the benchmark</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>4.71x</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>SCEM prints an unchanged close on 29.3% of sessions, 3.4x the Egyptian panel median and 2nd thinnest of 33 names. On such a series the benchmark's own volatility estimate collapses in quiet quarters.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Consequence</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>The map is ILLUSTRATIVE ONLY. It is materially too wide and must not be read with the confidence of a calibrated name.</t>
         </is>
@@ -2615,7 +2538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>Explicit WACC (rows) × terminal growth (columns) — fair value per share (EGP)</t>
         </is>
@@ -2654,19 +2577,19 @@
         <v>0.2529921630262293</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>47.84885020488337</v>
+        <v>47.85239987575165</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>46.42439256390911</v>
+        <v>46.42807849453837</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>44.78393251379664</v>
+        <v>44.78777410811193</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>42.87804730956334</v>
+        <v>42.88206844733539</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>40.64083805775741</v>
+        <v>40.64506858524987</v>
       </c>
     </row>
     <row r="7">
@@ -2674,19 +2597,19 @@
         <v>0.2679921630262292</v>
       </c>
       <c r="B7" s="18" t="n">
-        <v>47.27428754847774</v>
+        <v>47.27776652657919</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>45.88622828050651</v>
+        <v>45.88984005753007</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>44.28766207633895</v>
+        <v>44.29142556215732</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>42.43042427686677</v>
+        <v>42.4343627432738</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>40.25029345683448</v>
+        <v>40.25443599024933</v>
       </c>
     </row>
     <row r="8">
@@ -2694,19 +2617,19 @@
         <v>0.2829921630262293</v>
       </c>
       <c r="B8" s="18" t="n">
-        <v>46.71793045432781</v>
+        <v>46.72134103353847</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>45.36503894394706</v>
+        <v>45.36857897793945</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>43.80695054074625</v>
+        <v>43.81063846201682</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>41.99671621018461</v>
+        <v>42.0005747030714</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>39.87173537987529</v>
+        <v>39.87579279659943</v>
       </c>
     </row>
     <row r="9">
@@ -2714,19 +2637,19 @@
         <v>0.2979921630262293</v>
       </c>
       <c r="B9" s="18" t="n">
-        <v>46.17902668304209</v>
+        <v>46.18237106147301</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>44.86012465585996</v>
+        <v>44.8635952566741</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>43.34115822808959</v>
+        <v>43.34477302237466</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>41.5763533327626</v>
+        <v>41.58013443704983</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>39.50467604078285</v>
+        <v>39.50865109765196</v>
       </c>
     </row>
     <row r="10">
@@ -2734,23 +2657,23 @@
         <v>0.3129921630262292</v>
       </c>
       <c r="B10" s="18" t="n">
-        <v>45.65686220458439</v>
+        <v>45.66014248947234</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>44.37082102729465</v>
+        <v>44.37422440920808</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>42.88967786277495</v>
+        <v>42.89322186668822</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>41.16879466592241</v>
+        <v>41.17250085938183</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>39.14865222307241</v>
+        <v>39.1525475625393</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>NET CASH — the largest single uncertainty, now sensitised</t>
         </is>
@@ -2785,25 +2708,25 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>Fair value per share (EGP)</t>
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>38.05569194585932</v>
+        <v>38.05937986712988</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>40.93132124330279</v>
+        <v>40.93500916457335</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>43.80695054074625</v>
+        <v>43.81063846201682</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>46.68257983818972</v>
+        <v>46.68626775946028</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>49.55820913563318</v>
+        <v>49.56189705690375</v>
       </c>
     </row>
     <row r="16">
@@ -2821,7 +2744,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>Beta — fair value per share (EGP)</t>
         </is>
@@ -2856,29 +2779,29 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="41" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>Fair value</t>
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>48.90907393961128</v>
+        <v>48.91357507019821</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>46.08371760922441</v>
+        <v>46.08776877600348</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>45.62627476231599</v>
+        <v>45.63025299419375</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>43.80695054074625</v>
+        <v>43.81063846201682</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>41.11738933237334</v>
+        <v>41.12064739648515</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>EBITDA margin shift — fair value per share (EGP)</t>
         </is>
@@ -2913,25 +2836,25 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="41" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>Fair value</t>
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>35.56363456632703</v>
+        <v>35.56710249338433</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>39.6728693813603</v>
+        <v>39.67644904785723</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>43.80695054074625</v>
+        <v>43.81063846201682</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>47.67547519425753</v>
+        <v>47.67735945226617</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>49.79280011722686</v>
+        <v>49.7950196365083</v>
       </c>
     </row>
     <row r="28">
@@ -3100,23 +3023,23 @@
         </is>
       </c>
       <c r="E6" s="15">
-        <f>'Cash Flow'!E15/Assumptions!$B$6</f>
+        <f>'Cash Flow'!E13/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F6" s="15">
-        <f>'Cash Flow'!F15/Assumptions!$B$6</f>
+        <f>'Cash Flow'!F13/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="G6" s="15">
-        <f>'Cash Flow'!G15/Assumptions!$B$6</f>
+        <f>'Cash Flow'!G13/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="H6" s="15">
-        <f>'Cash Flow'!H15/Assumptions!$B$6</f>
+        <f>'Cash Flow'!H13/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="I6" s="15">
-        <f>'Cash Flow'!I15/Assumptions!$B$6</f>
+        <f>'Cash Flow'!I13/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3270,36 +3193,28 @@
           <t>EBITDA per tonne sold (EGP)</t>
         </is>
       </c>
-      <c r="B11" s="29">
-        <f>'Income Statement'!B6/'Unit Build'!B10</f>
-        <v/>
-      </c>
-      <c r="C11" s="29">
-        <f>'Income Statement'!C6/'Unit Build'!C10</f>
-        <v/>
-      </c>
-      <c r="D11" s="29">
-        <f>'Income Statement'!D6/'Unit Build'!D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="29">
-        <f>'Income Statement'!E6/'Unit Build'!E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="29">
-        <f>'Income Statement'!F6/'Unit Build'!F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="29">
-        <f>'Income Statement'!G6/'Unit Build'!G10</f>
-        <v/>
-      </c>
-      <c r="H11" s="29">
-        <f>'Income Statement'!H6/'Unit Build'!H10</f>
-        <v/>
-      </c>
-      <c r="I11" s="29">
-        <f>'Income Statement'!I6/'Unit Build'!I10</f>
+      <c r="D11" s="30">
+        <f>'Income Statement'!D6/'Summary Financials'!D9</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>'Income Statement'!E6/'Summary Financials'!E9</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>'Income Statement'!F6/'Summary Financials'!F9</f>
+        <v/>
+      </c>
+      <c r="G11" s="30">
+        <f>'Income Statement'!G6/'Summary Financials'!G9</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>'Income Statement'!H6/'Summary Financials'!H9</f>
+        <v/>
+      </c>
+      <c r="I11" s="30">
+        <f>'Income Statement'!I6/'Summary Financials'!I9</f>
         <v/>
       </c>
     </row>
@@ -3309,35 +3224,35 @@
           <t>Price / earnings (at spot)</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="32">
         <f>Assumptions!$B$5/B5</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>Assumptions!$B$5/C5</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>Assumptions!$B$5/D5</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>Assumptions!$B$5/E5</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>Assumptions!$B$5/F5</f>
         <v/>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="32">
         <f>Assumptions!$B$5/G5</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="32">
         <f>Assumptions!$B$5/H5</f>
         <v/>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="32">
         <f>Assumptions!$B$5/I5</f>
         <v/>
       </c>
@@ -3348,35 +3263,35 @@
           <t>EV / EBITDA (at spot)</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!B7-'Balance Sheet'!B9))/'Income Statement'!B6</f>
         <v/>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!C7-'Balance Sheet'!C9))/'Income Statement'!C6</f>
         <v/>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!D7-'Balance Sheet'!D9))/'Income Statement'!D6</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!E7-'Balance Sheet'!E9))/'Income Statement'!E6</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!F7-'Balance Sheet'!F9))/'Income Statement'!F6</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!G7-'Balance Sheet'!G9))/'Income Statement'!G6</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!H7-'Balance Sheet'!H9))/'Income Statement'!H6</f>
         <v/>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="32">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!I7-'Balance Sheet'!I9))/'Income Statement'!I6</f>
         <v/>
       </c>
@@ -3451,7 +3366,7 @@
           <t>Misr Beni Suef — FY2025 net sales (EGP mn)</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="23" t="n">
         <v>5700</v>
       </c>
     </row>
@@ -3461,7 +3376,7 @@
           <t>Misr Beni Suef — FY2025 attributable profit (EGP mn)</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>3946</v>
       </c>
     </row>
@@ -3481,7 +3396,7 @@
           <t>Misr Beni Suef — market capitalisation (EGP mn)</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>13730</v>
       </c>
     </row>
@@ -3511,7 +3426,7 @@
           <t>Arabian Cement — FY2025 consolidated profit (EGP mn)</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -3605,7 +3520,7 @@
           <t>Structural surplus (capacity less consumption, Mt)</t>
         </is>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="33">
         <f>B14-B15</f>
         <v/>
       </c>
@@ -3616,7 +3531,7 @@
           <t>SCEM EV/EBITDA at spot on FY2026E</t>
         </is>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <f>'Per-Share &amp; Ratios'!E13</f>
         <v/>
       </c>
@@ -4077,7 +3992,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>'Relative &amp; Normalized'!B12</f>
+        <f>'Relative &amp; Normalized'!B15</f>
         <v/>
       </c>
       <c r="C6" s="11">
@@ -4096,7 +4011,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>'Relative &amp; Normalized'!B22</f>
+        <f>'Relative &amp; Normalized'!B26</f>
         <v/>
       </c>
       <c r="C7" s="11">
@@ -4115,7 +4030,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>'Relative &amp; Normalized'!B33</f>
+        <f>'Relative &amp; Normalized'!B38</f>
         <v/>
       </c>
       <c r="C8" s="11">
@@ -4389,6 +4304,21 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Clinker factor</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>0.6763</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>t clinker / t cement</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -4440,7 +4370,7 @@
           <t>Specific electrical energy</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="23" t="n">
         <v>100</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -4470,7 +4400,7 @@
           <t>Raw materials &amp; quarrying</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="23" t="n">
         <v>190</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4485,7 +4415,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="23" t="n">
         <v>55</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -4510,7 +4440,7 @@
           <t>Distribution &amp; selling</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="23" t="n">
         <v>250</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -4638,22 +4568,22 @@
           <t>Domestic realised price</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="23" t="n">
         <v>3503</v>
       </c>
-      <c r="C30" s="22" t="n">
+      <c r="C30" s="23" t="n">
         <v>3713</v>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="23" t="n">
         <v>3880</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="23" t="n">
         <v>4074</v>
       </c>
-      <c r="F30" s="22" t="n">
+      <c r="F30" s="23" t="n">
         <v>4297</v>
       </c>
-      <c r="G30" s="22" t="n">
+      <c r="G30" s="23" t="n">
         <v>4512</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -4723,22 +4653,22 @@
           <t>Local cost inflation index</t>
         </is>
       </c>
-      <c r="B33" s="23" t="n">
+      <c r="B33" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="22" t="n">
         <v>1.14</v>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="22" t="n">
         <v>1.265</v>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="22" t="n">
         <v>1.365</v>
       </c>
-      <c r="F33" s="23" t="n">
+      <c r="F33" s="22" t="n">
         <v>1.45</v>
       </c>
-      <c r="G33" s="23" t="n">
+      <c r="G33" s="22" t="n">
         <v>1.53</v>
       </c>
     </row>
@@ -5011,7 +4941,7 @@
           <t>Elapsed fraction of FY2026 at valuation</t>
         </is>
       </c>
-      <c r="B56" s="23" t="n">
+      <c r="B56" s="22" t="n">
         <v>0.583</v>
       </c>
     </row>
@@ -5036,7 +4966,7 @@
           <t>FY2025 cash (REPORTED)</t>
         </is>
       </c>
-      <c r="B59" s="22" t="n">
+      <c r="B59" s="23" t="n">
         <v>3850</v>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -5051,7 +4981,7 @@
           <t>FY2025 equity (reported)</t>
         </is>
       </c>
-      <c r="B60" s="22" t="n">
+      <c r="B60" s="23" t="n">
         <v>5240</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -5066,7 +4996,7 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B61" s="22" t="n">
+      <c r="B61" s="23" t="n">
         <v>120</v>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -5081,7 +5011,7 @@
           <t>FY2023 revenue</t>
         </is>
       </c>
-      <c r="B62" s="22" t="n">
+      <c r="B62" s="23" t="n">
         <v>4280</v>
       </c>
     </row>
@@ -5091,7 +5021,7 @@
           <t>FY2024 revenue</t>
         </is>
       </c>
-      <c r="B63" s="22" t="n">
+      <c r="B63" s="23" t="n">
         <v>6420</v>
       </c>
     </row>
@@ -5101,7 +5031,7 @@
           <t>FY2025 revenue</t>
         </is>
       </c>
-      <c r="B64" s="22" t="n">
+      <c r="B64" s="23" t="n">
         <v>9090</v>
       </c>
     </row>
@@ -5111,7 +5041,7 @@
           <t>FY2023 profit after tax</t>
         </is>
       </c>
-      <c r="B65" s="22" t="n">
+      <c r="B65" s="23" t="n">
         <v>-121.42</v>
       </c>
     </row>
@@ -5121,7 +5051,7 @@
           <t>FY2024 profit after tax</t>
         </is>
       </c>
-      <c r="B66" s="22" t="n">
+      <c r="B66" s="23" t="n">
         <v>3070</v>
       </c>
     </row>
@@ -5131,7 +5061,7 @@
           <t>FY2025 profit after tax</t>
         </is>
       </c>
-      <c r="B67" s="22" t="n">
+      <c r="B67" s="23" t="n">
         <v>2290</v>
       </c>
     </row>
@@ -5141,7 +5071,7 @@
           <t>FY2024 EBITDA (disclosed anchor)</t>
         </is>
       </c>
-      <c r="B68" s="22" t="n">
+      <c r="B68" s="23" t="n">
         <v>1590</v>
       </c>
     </row>
@@ -5171,7 +5101,7 @@
           <t>FY2023 treasury income</t>
         </is>
       </c>
-      <c r="B71" s="22" t="n">
+      <c r="B71" s="23" t="n">
         <v>198</v>
       </c>
     </row>
@@ -5271,7 +5201,7 @@
           <t>Replacement cost of capacity</t>
         </is>
       </c>
-      <c r="B80" s="22" t="n">
+      <c r="B80" s="23" t="n">
         <v>130</v>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -5286,7 +5216,7 @@
           <t>Justified EV per tonne</t>
         </is>
       </c>
-      <c r="B81" s="22" t="n">
+      <c r="B81" s="23" t="n">
         <v>95</v>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -5432,7 +5362,7 @@
           <t>Sinai White stake — carrying value</t>
         </is>
       </c>
-      <c r="B94" s="22" t="n">
+      <c r="B94" s="23" t="n">
         <v>100</v>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -5848,28 +5778,28 @@
           <t>Clinker factor (t clinker / t cement)</t>
         </is>
       </c>
-      <c r="B9" s="27">
-        <f>B5/B8</f>
-        <v/>
-      </c>
-      <c r="C9" s="27">
-        <f>C5/C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="27">
-        <f>D5/D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="27">
-        <f>E5/E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="27">
-        <f>F5/F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="27">
-        <f>G5/G8</f>
+      <c r="B9" s="28">
+        <f>Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C9" s="28">
+        <f>Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D9" s="28">
+        <f>Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E9" s="28">
+        <f>Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="F9" s="28">
+        <f>Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="G9" s="28">
+        <f>Assumptions!$B$14</f>
         <v/>
       </c>
     </row>
@@ -6034,27 +5964,27 @@
           <t>Export price (USD/t)</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="29">
         <f>Assumptions!$B$31</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>Assumptions!$C$31</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>Assumptions!$D$31</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>Assumptions!$E$31</f>
         <v/>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>Assumptions!$F$31</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>Assumptions!$G$31</f>
         <v/>
       </c>
@@ -6065,27 +5995,27 @@
           <t>USD/EGP</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>Assumptions!$B$32</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>Assumptions!$D$32</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>Assumptions!$E$32</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>Assumptions!$F$32</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>Assumptions!$G$32</f>
         <v/>
       </c>
@@ -6096,27 +6026,27 @@
           <t>Domestic revenue (EGP mn)</t>
         </is>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <f>B12*B14</f>
         <v/>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>C12*C14</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>D12*D14</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>E12*E14</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>F12*F14</f>
         <v/>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="30">
         <f>G12*G14</f>
         <v/>
       </c>
@@ -6127,27 +6057,27 @@
           <t>Export revenue (EGP mn)</t>
         </is>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <f>B13*B15*B16</f>
         <v/>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>C13*C15*C16</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>D13*D15*D16</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>E13*E15*E16</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <f>F13*F15*F16</f>
         <v/>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="30">
         <f>G13*G15*G16</f>
         <v/>
       </c>
@@ -6158,27 +6088,27 @@
           <t>REVENUE (EGP mn)</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="31">
         <f>G17+G18</f>
         <v/>
       </c>
@@ -6189,27 +6119,27 @@
           <t>Blended realised price (EGP/t)</t>
         </is>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <f>B19/B10</f>
         <v/>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>C19/C10</f>
         <v/>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>D19/D10</f>
         <v/>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>E19/E10</f>
         <v/>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f>F19/F10</f>
         <v/>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="30">
         <f>G19/G10</f>
         <v/>
       </c>
@@ -6236,27 +6166,27 @@
           <t>Thermal fuel</t>
         </is>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="30">
         <f>Assumptions!$B$16*B9*Assumptions!$B$17*B16</f>
         <v/>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <f>Assumptions!$B$16*C9*Assumptions!$B$17*C16</f>
         <v/>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <f>Assumptions!$B$16*D9*Assumptions!$B$17*D16</f>
         <v/>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <f>Assumptions!$B$16*E9*Assumptions!$B$17*E16</f>
         <v/>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <f>Assumptions!$B$16*F9*Assumptions!$B$17*F16</f>
         <v/>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <f>Assumptions!$B$16*G9*Assumptions!$B$17*G16</f>
         <v/>
       </c>
@@ -6267,27 +6197,27 @@
           <t>Electrical power</t>
         </is>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="30">
         <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$C$33</f>
         <v/>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$D$33</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$E$33</f>
         <v/>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$F$33</f>
         <v/>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$G$33</f>
         <v/>
       </c>
@@ -6298,27 +6228,27 @@
           <t>Raw materials &amp; quarrying</t>
         </is>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="30">
         <f>Assumptions!$B$20*Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>Assumptions!$B$20*Assumptions!$C$33</f>
         <v/>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <f>Assumptions!$B$20*Assumptions!$D$33</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>Assumptions!$B$20*Assumptions!$E$33</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <f>Assumptions!$B$20*Assumptions!$F$33</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <f>Assumptions!$B$20*Assumptions!$G$33</f>
         <v/>
       </c>
@@ -6329,27 +6259,27 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="30">
         <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$C$33</f>
         <v/>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$D$33</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$E$33</f>
         <v/>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$F$33</f>
         <v/>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="30">
         <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$G$33</f>
         <v/>
       </c>
@@ -6360,27 +6290,27 @@
           <t>Distribution &amp; selling</t>
         </is>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <f>Assumptions!$B$23*Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <f>Assumptions!$B$23*Assumptions!$C$33</f>
         <v/>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <f>Assumptions!$B$23*Assumptions!$D$33</f>
         <v/>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <f>Assumptions!$B$23*Assumptions!$E$33</f>
         <v/>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="30">
         <f>Assumptions!$B$23*Assumptions!$F$33</f>
         <v/>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="30">
         <f>Assumptions!$B$23*Assumptions!$G$33</f>
         <v/>
       </c>
@@ -6391,27 +6321,27 @@
           <t>TOTAL VARIABLE (EGP/t)</t>
         </is>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="31">
         <f>SUM(B23:B27)</f>
         <v/>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <f>SUM(C23:C27)</f>
         <v/>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="31">
         <f>SUM(D23:D27)</f>
         <v/>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="31">
         <f>SUM(E23:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="31">
         <f>SUM(F23:F27)</f>
         <v/>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="31">
         <f>SUM(G23:G27)</f>
         <v/>
       </c>
@@ -6469,27 +6399,27 @@
           <t>Variable cost</t>
         </is>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="30">
         <f>B28*B10</f>
         <v/>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <f>C28*C10</f>
         <v/>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <f>D28*D10</f>
         <v/>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="30">
         <f>E28*E10</f>
         <v/>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="30">
         <f>F28*F10</f>
         <v/>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="30">
         <f>G28*G10</f>
         <v/>
       </c>
@@ -6500,27 +6430,27 @@
           <t>Fixed cost</t>
         </is>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="30">
         <f>Assumptions!$B$24*B8*Assumptions!$B$9*Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="30">
         <f>Assumptions!$B$24*C8*Assumptions!$B$9*Assumptions!$C$33</f>
         <v/>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="30">
         <f>Assumptions!$B$24*D8*Assumptions!$B$9*Assumptions!$D$33</f>
         <v/>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="30">
         <f>Assumptions!$B$24*E8*Assumptions!$B$9*Assumptions!$E$33</f>
         <v/>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="30">
         <f>Assumptions!$B$24*F8*Assumptions!$B$9*Assumptions!$F$33</f>
         <v/>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="30">
         <f>Assumptions!$B$24*G8*Assumptions!$B$9*Assumptions!$G$33</f>
         <v/>
       </c>
@@ -6531,27 +6461,27 @@
           <t>EBITDA  (AN OUTPUT)</t>
         </is>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="31">
         <f>B31-B32-B33</f>
         <v/>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="31">
         <f>C31-C32-C33</f>
         <v/>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="31">
         <f>D31-D32-D33</f>
         <v/>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="31">
         <f>E31-E32-E33</f>
         <v/>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="31">
         <f>F31-F32-F33</f>
         <v/>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="31">
         <f>G31-G32-G33</f>
         <v/>
       </c>
@@ -6593,27 +6523,27 @@
           <t>EBITDA per tonne (EGP)</t>
         </is>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="30">
         <f>B34/B10</f>
         <v/>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="30">
         <f>C34/C10</f>
         <v/>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="30">
         <f>D34/D10</f>
         <v/>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="30">
         <f>E34/E10</f>
         <v/>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="30">
         <f>F34/F10</f>
         <v/>
       </c>
-      <c r="G36" s="29">
+      <c r="G36" s="30">
         <f>G34/G10</f>
         <v/>
       </c>
@@ -6640,7 +6570,7 @@
           <t>Bottom-up FY2025 revenue</t>
         </is>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="30">
         <f>B19</f>
         <v/>
       </c>
@@ -6673,7 +6603,7 @@
           <t>Bottom-up FY2025 EBITDA</t>
         </is>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="30">
         <f>B34</f>
         <v/>
       </c>
@@ -6745,7 +6675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6783,32 +6713,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY2025 revenue</t>
-        </is>
-      </c>
-      <c r="B5" s="29">
-        <f>'Unit Build'!D10</f>
+          <t>FY2025 revenue (disclosed)</t>
+        </is>
+      </c>
+      <c r="B5" s="30">
+        <f>Assumptions!$B$64</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA margin</t>
+          <t>Normalised revenue haircut</t>
         </is>
       </c>
       <c r="B6" s="12">
-        <f>Assumptions!$B$84</f>
+        <f>Assumptions!$B$85</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Normalised EBITDA</t>
-        </is>
-      </c>
-      <c r="B7" s="29">
+          <t>Normalised revenue base</t>
+        </is>
+      </c>
+      <c r="B7" s="30">
         <f>B5*B6</f>
         <v/>
       </c>
@@ -6816,21 +6746,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B8" s="31">
-        <f>Assumptions!$B$82</f>
+          <t>Mid-cycle EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>Assumptions!$B$84</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Implied enterprise value</t>
-        </is>
-      </c>
-      <c r="B9" s="29">
+          <t>Normalised EBITDA</t>
+        </is>
+      </c>
+      <c r="B9" s="30">
         <f>B7*B8</f>
         <v/>
       </c>
@@ -6838,110 +6768,110 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Plus net cash</t>
-        </is>
-      </c>
-      <c r="B10" s="29">
-        <f>DCF!B36</f>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B10" s="32">
+        <f>Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Implied equity value</t>
-        </is>
-      </c>
-      <c r="B11" s="29">
-        <f>B9+B10</f>
+          <t>Implied enterprise value</t>
+        </is>
+      </c>
+      <c r="B11" s="30">
+        <f>B9*B10</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
-        </is>
-      </c>
-      <c r="B12" s="13">
-        <f>B11/Assumptions!$B$6</f>
+          <t>Plus net cash</t>
+        </is>
+      </c>
+      <c r="B12" s="30">
+        <f>DCF!B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Less non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B13" s="30">
+        <f>-Assumptions!$B$61</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>NORMALISED EARNINGS POWER</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Implied equity value</t>
+        </is>
+      </c>
+      <c r="B14" s="30">
+        <f>B11+B12+B13</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Normalised EBITDA</t>
-        </is>
-      </c>
-      <c r="B15" s="29">
-        <f>B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Less D&amp;A (FY2025)</t>
-        </is>
-      </c>
-      <c r="B16" s="29">
-        <f>-'Income Statement'!D8</f>
+          <t>Implied value per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B15" s="13">
+        <f>B14/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Normalised EBIT</t>
-        </is>
-      </c>
-      <c r="B17" s="29">
-        <f>B15+B16</f>
-        <v/>
-      </c>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>NORMALISED EARNINGS POWER</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Normalised NOPAT</t>
-        </is>
-      </c>
-      <c r="B18" s="29">
-        <f>B17*(1-Assumptions!$B$7)</f>
+          <t>Normalised EBITDA</t>
+        </is>
+      </c>
+      <c r="B18" s="30">
+        <f>B9</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Plus after-tax treasury income</t>
-        </is>
-      </c>
-      <c r="B19" s="29">
-        <f>DCF!B36*Assumptions!$D$39*(1-Assumptions!$B$7)</f>
+          <t>Less D&amp;A (FY2025)</t>
+        </is>
+      </c>
+      <c r="B19" s="30">
+        <f>-'Income Statement'!D8</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Normalised earnings</t>
-        </is>
-      </c>
-      <c r="B20" s="29">
+          <t>Normalised EBIT</t>
+        </is>
+      </c>
+      <c r="B20" s="30">
         <f>B18+B19</f>
         <v/>
       </c>
@@ -6949,193 +6879,248 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="B21" s="31">
-        <f>Assumptions!$B$83</f>
+          <t>Normalised NOPAT</t>
+        </is>
+      </c>
+      <c r="B21" s="30">
+        <f>B20*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
-        </is>
-      </c>
-      <c r="B22" s="13">
-        <f>B20*B21/Assumptions!$B$6</f>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="B22" s="32">
+        <f>Assumptions!$B$83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Operating equity value</t>
+        </is>
+      </c>
+      <c r="B23" s="30">
+        <f>B21*B22</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>ASSET LENS — EV PER TONNE OF CAPACITY (the cement sector yardstick)</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Plus net cash AT FACE (not capitalised)</t>
+        </is>
+      </c>
+      <c r="B24" s="30">
+        <f>DCF!B36</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Enterprise value at spot (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B25" s="29">
-        <f>Assumptions!$B$5*Assumptions!$B$6-DCF!B36</f>
+          <t>Less non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B25" s="30">
+        <f>-Assumptions!$B$61</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Capacity (annual tonnes)</t>
-        </is>
-      </c>
-      <c r="B26" s="29">
-        <f>Assumptions!$B$12*1000000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>EV per tonne at spot (USD/t)</t>
-        </is>
-      </c>
-      <c r="B27" s="32">
-        <f>B25*1000000/B26/Assumptions!$B$9</f>
+          <t>Implied value per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B26" s="13">
+        <f>(B23+B24+B25)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Replacement cost (USD/t)</t>
-        </is>
-      </c>
-      <c r="B28" s="29">
-        <f>Assumptions!$B$80</f>
-        <v/>
-      </c>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>ASSET LENS — EV PER TONNE OF CAPACITY (the cement sector yardstick)</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Discount to replacement cost</t>
-        </is>
-      </c>
-      <c r="B29" s="12">
-        <f>B27/B28-1</f>
+          <t>Enterprise value at spot (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B29" s="30">
+        <f>Assumptions!$B$5*Assumptions!$B$6-DCF!B36</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Justified EV per tonne (USD/t)</t>
-        </is>
-      </c>
-      <c r="B30" s="29">
-        <f>Assumptions!$B$81</f>
+          <t>Capacity (annual tonnes)</t>
+        </is>
+      </c>
+      <c r="B30" s="30">
+        <f>Assumptions!$B$12*1000000</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Implied enterprise value (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B31" s="29">
-        <f>B30*B26*Assumptions!$B$9/1000000</f>
+          <t>EV per tonne at spot (USD/t)</t>
+        </is>
+      </c>
+      <c r="B31" s="33">
+        <f>B29*1000000/B30/Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Plus net cash</t>
-        </is>
-      </c>
-      <c r="B32" s="29">
-        <f>DCF!B36</f>
+          <t>Replacement cost (USD/t)</t>
+        </is>
+      </c>
+      <c r="B32" s="30">
+        <f>Assumptions!$B$80</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
-        </is>
-      </c>
-      <c r="B33" s="13">
-        <f>(B31+B32)/Assumptions!$B$6</f>
+          <t>Discount to replacement cost</t>
+        </is>
+      </c>
+      <c r="B33" s="12">
+        <f>B31/B32-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Justified EV per tonne (USD/t)</t>
+        </is>
+      </c>
+      <c r="B34" s="30">
+        <f>Assumptions!$B$81</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>MEMO — BOOK, SHOWN BUT NOT USED AS A LENS</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Implied enterprise value (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B35" s="30">
+        <f>B34*B30*Assumptions!$B$9/1000000</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Book value per share (EGP)</t>
-        </is>
-      </c>
-      <c r="B36" s="15">
-        <f>'Balance Sheet'!D12/Assumptions!$B$6</f>
+          <t>Plus net cash</t>
+        </is>
+      </c>
+      <c r="B36" s="30">
+        <f>DCF!B36</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Less non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B37" s="31">
+        <f>-Assumptions!$B$61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Implied value per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B38" s="15">
+        <f>(B35+B36+B37)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>MEMO — BOOK, SHOWN BUT NOT USED AS A LENS</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Book value per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B41" s="15">
+        <f>'Balance Sheet'!D12/Assumptions!$B$74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="B37" s="12">
-        <f>B18/'Balance Sheet'!D12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="B42" s="12">
+        <f>B21/'Balance Sheet'!D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>A book/return lens is deliberately NOT one of the four. The El Hassana plant commissioned in 1997 and</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>is carried at historic cost through a five-fold devaluation, so book value measures the accounting</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>rather than the asset. The cement sector's own yardstick — enterprise value per annual tonne of</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>capacity against replacement cost — is used in its place.</t>
         </is>
@@ -7143,10 +7128,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A46:J46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7307,23 +7292,23 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <f>B5*Assumptions!$B$36</f>
         <v/>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>C5*Assumptions!$C$36</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>D5*Assumptions!$D$36</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>E5*Assumptions!$E$36</f>
         <v/>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>F5*Assumptions!$F$36</f>
         <v/>
       </c>
@@ -7334,23 +7319,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>B7-B8</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>F7-F8</f>
         <v/>
       </c>
@@ -7388,23 +7373,23 @@
           <t>NOPAT  (EBIT × (1 − t))</t>
         </is>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>B9*(1-B10)</f>
         <v/>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>C9*(1-C10)</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>D9*(1-D10)</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>E9*(1-E10)</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>F9*(1-F10)</f>
         <v/>
       </c>
@@ -7415,23 +7400,23 @@
           <t>Memo: capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <f>B5*Assumptions!$B$37</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>C5*Assumptions!$C$37</f>
         <v/>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>D5*Assumptions!$D$37</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>E5*Assumptions!$E$37</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>F5*Assumptions!$F$37</f>
         <v/>
       </c>
@@ -7442,23 +7427,23 @@
           <t>Memo: change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="29">
-        <f>(B5-'Unit Build'!B31)*Assumptions!$B$40</f>
-        <v/>
-      </c>
-      <c r="C13" s="29">
+      <c r="B13" s="30">
+        <f>(B5-Assumptions!$B$64)*Assumptions!$B$40</f>
+        <v/>
+      </c>
+      <c r="C13" s="30">
         <f>(C5-B5)*Assumptions!$B$40</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>(D5-C5)*Assumptions!$B$40</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>(E5-D5)*Assumptions!$B$40</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>(F5-E5)*Assumptions!$B$40</f>
         <v/>
       </c>
@@ -7469,23 +7454,23 @@
           <t>Net reinvestment  (growth ÷ terminal ROIC)</t>
         </is>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <f>MAX(B11-$B$23,0)/$B$24</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>MAX(C11-B11,0)/$B$24</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>MAX(D11-C11,0)/$B$24</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>MAX(E11-D11,0)/$B$24</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>MAX(F11-E11,0)/$B$24</f>
         <v/>
       </c>
@@ -7496,23 +7481,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <f>(B11-B14)*(1-Assumptions!$B$56)</f>
         <v/>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>C11-C14</f>
         <v/>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <f>D11-D14</f>
         <v/>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>E11-E14</f>
         <v/>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>F11-F14</f>
         <v/>
       </c>
@@ -7523,23 +7508,23 @@
           <t>Glide fraction</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="34">
         <f>(Assumptions!$B$38-Assumptions!$B$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
         <v/>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="34">
         <f>(Assumptions!$B$38-Assumptions!$C$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
         <v/>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="34">
         <f>(Assumptions!$B$38-Assumptions!$D$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
         <v/>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>(Assumptions!$B$38-Assumptions!$E$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
         <v/>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="34">
         <f>(Assumptions!$B$38-Assumptions!$F$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
         <v/>
       </c>
@@ -7550,23 +7535,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="35">
         <f>$C$46-($C$46-$C$53)*B16</f>
         <v/>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="35">
         <f>$C$46-($C$46-$C$53)*C16</f>
         <v/>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="35">
         <f>$C$46-($C$46-$C$53)*D16</f>
         <v/>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="35">
         <f>$C$46-($C$46-$C$53)*E16</f>
         <v/>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="35">
         <f>$C$46-($C$46-$C$53)*F16</f>
         <v/>
       </c>
@@ -7577,23 +7562,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="34">
         <f>1/(1+B17)^((1-Assumptions!$B$56)/2)</f>
         <v/>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="34">
         <f>1/(1+B17)^(1-Assumptions!$B$56+0.5)</f>
         <v/>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="34">
         <f>1/((1+B17)*(1+C17)^(1-Assumptions!$B$56+0.5))</f>
         <v/>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <f>1/((1+B17)*(1+C17)*(1+D17)^(1-Assumptions!$B$56+0.5))</f>
         <v/>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="34">
         <f>1/((1+B17)*(1+C17)*(1+D17)*(1+E17)^(1-Assumptions!$B$56+0.5))</f>
         <v/>
       </c>
@@ -7604,23 +7589,23 @@
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <f>B15*B18</f>
         <v/>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>C15*C18</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <f>D15*D18</f>
         <v/>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <f>E15*E18</f>
         <v/>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <f>F15*F18</f>
         <v/>
       </c>
@@ -7645,7 +7630,7 @@
           <t>Replacement-cost invested capital (EGP mn)</t>
         </is>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <f>Assumptions!$B$12*1000000*Assumptions!$B$80*Assumptions!$B$9/1000000</f>
         <v/>
       </c>
@@ -7656,7 +7641,7 @@
           <t>FY2025 NOPAT (the reinvestment base)</t>
         </is>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="30">
         <f>('Income Statement'!D6-'Income Statement'!D8)*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
@@ -7689,7 +7674,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="30">
         <f>B28*(1-B25)/($C$53-Assumptions!$B$55)</f>
         <v/>
       </c>
@@ -7700,7 +7685,7 @@
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <f>B26*F18</f>
         <v/>
       </c>
@@ -7711,7 +7696,7 @@
           <t>Terminal NOPAT</t>
         </is>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="30">
         <f>F11*(1+Assumptions!$B$55)</f>
         <v/>
       </c>
@@ -7736,7 +7721,7 @@
           <t>Present value of explicit years (FY2026E-FY2030E)</t>
         </is>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="30">
         <f>SUM(B19:F19)</f>
         <v/>
       </c>
@@ -7747,7 +7732,7 @@
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="30">
         <f>B27</f>
         <v/>
       </c>
@@ -7758,7 +7743,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="31">
         <f>B30+B31</f>
         <v/>
       </c>
@@ -7780,8 +7765,8 @@
           <t>Cash at the valuation date</t>
         </is>
       </c>
-      <c r="B34" s="29">
-        <f>'Balance Sheet'!D7</f>
+      <c r="B34" s="30">
+        <f>'Balance Sheet'!D7+B15/(1-Assumptions!$B$56)*Assumptions!$B$56</f>
         <v/>
       </c>
     </row>
@@ -7791,7 +7776,7 @@
           <t>Less gross debt</t>
         </is>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>-Assumptions!$B$50</f>
         <v/>
       </c>
@@ -7802,7 +7787,7 @@
           <t>Net cash (ADDED — the company is net cash)</t>
         </is>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="30">
         <f>B34+B35</f>
         <v/>
       </c>
@@ -7813,7 +7798,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="31">
         <f>B32+B36-B40</f>
         <v/>
       </c>
@@ -7824,7 +7809,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B38" s="35">
+      <c r="B38" s="36">
         <f>Assumptions!$B$6</f>
         <v/>
       </c>
@@ -7846,7 +7831,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="30">
         <f>Assumptions!$B$61</f>
         <v/>
       </c>
@@ -7871,7 +7856,7 @@
           <t>Risk-free rate (observed EGP 10-year)</t>
         </is>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="35">
         <f>Assumptions!$B$45</f>
         <v/>
       </c>
@@ -7882,7 +7867,7 @@
           <t>Less sovereign default spread</t>
         </is>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="35">
         <f>-Assumptions!$B$46</f>
         <v/>
       </c>
@@ -7893,7 +7878,7 @@
           <t>Normalised risk-free rate</t>
         </is>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="35">
         <f>C42+C43</f>
         <v/>
       </c>
@@ -7904,7 +7889,7 @@
           <t>Cost of equity  (rf* + β × ERP)</t>
         </is>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="35">
         <f>C44+Assumptions!$B$48*Assumptions!$B$47</f>
         <v/>
       </c>
@@ -7915,7 +7900,7 @@
           <t>WACC — explicit window</t>
         </is>
       </c>
-      <c r="C46" s="36">
+      <c r="C46" s="37">
         <f>(1-C49)*C45+C49*C48</f>
         <v/>
       </c>
@@ -7926,7 +7911,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="35">
         <f>Assumptions!$B$49*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
@@ -7937,7 +7922,7 @@
           <t>Debt weight  D/(D+E)</t>
         </is>
       </c>
-      <c r="C49" s="37">
+      <c r="C49" s="38">
         <f>Assumptions!$B$50/(Assumptions!$B$50+C50)</f>
         <v/>
       </c>
@@ -7948,7 +7933,7 @@
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="30">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -7959,7 +7944,7 @@
           <t>Terminal cost of equity  (rf_term + β_L × ERP_term)</t>
         </is>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="35">
         <f>Assumptions!$B$51+C56*Assumptions!$B$52</f>
         <v/>
       </c>
@@ -7970,7 +7955,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C52" s="34">
+      <c r="C52" s="35">
         <f>Assumptions!$B$53*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
@@ -7981,7 +7966,7 @@
           <t>WACC — terminal</t>
         </is>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="37">
         <f>(1-Assumptions!$B$54)*C51+Assumptions!$B$54*C52</f>
         <v/>
       </c>
@@ -7992,7 +7977,7 @@
           <t>Retired construction: rf NOT netted (disclosed only)</t>
         </is>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="35">
         <f>Assumptions!$B$45+Assumptions!$B$48*Assumptions!$B$47</f>
         <v/>
       </c>
@@ -8003,7 +7988,7 @@
           <t>Sovereign double-count removed (bp)</t>
         </is>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="30">
         <f>(C54-C45)*10000</f>
         <v/>
       </c>
@@ -8160,15 +8145,15 @@
         </is>
       </c>
       <c r="B5" s="9">
-        <f>'Unit Build'!B11</f>
+        <f>Assumptions!$B$62</f>
         <v/>
       </c>
       <c r="C5" s="9">
-        <f>'Unit Build'!C11</f>
+        <f>Assumptions!$B$63</f>
         <v/>
       </c>
       <c r="D5" s="9">
-        <f>'Unit Build'!D11</f>
+        <f>Assumptions!$B$64</f>
         <v/>
       </c>
       <c r="E5" s="9">
@@ -8198,15 +8183,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <f>B9+B8</f>
         <v/>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <f>C9+C8</f>
         <v/>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>D9+D8</f>
         <v/>
       </c>
@@ -8276,15 +8261,15 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <f>B5*Assumptions!$B$75</f>
         <v/>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>C5*Assumptions!$B$76</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>D5*Assumptions!$B$77</f>
         <v/>
       </c>
@@ -8315,35 +8300,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>B14-B10</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>Assumptions!$B$68-C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D14/(1-Assumptions!$B$8)-D10</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>E6-E8</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>F6-F8</f>
         <v/>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <f>G6-G8</f>
         <v/>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="30">
         <f>H6-H8</f>
         <v/>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="30">
         <f>I6-I8</f>
         <v/>
       </c>
@@ -8358,31 +8343,31 @@
         <f>Assumptions!$B$71</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>Assumptions!$B$59/1.25*0.9*Assumptions!$B$42</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>(Assumptions!$B$59+Assumptions!$B$59/1.25)/2*Assumptions!$B$42</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>'Balance Sheet'!D7*Assumptions!$B$39</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>'Balance Sheet'!E7*Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>'Balance Sheet'!F7*Assumptions!$D$39</f>
         <v/>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <f>'Balance Sheet'!G7*Assumptions!$E$39</f>
         <v/>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="30">
         <f>'Balance Sheet'!H7*Assumptions!$F$39</f>
         <v/>
       </c>
@@ -8393,35 +8378,35 @@
           <t>Gain on disposal of Sinai White stake</t>
         </is>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>0</f>
         <v/>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>Assumptions!$B$92*Assumptions!$B$93-Assumptions!$B$94</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>0</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>0</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>0</f>
         <v/>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>0</f>
         <v/>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="30">
         <f>0</f>
         <v/>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="30">
         <f>0</f>
         <v/>
       </c>
@@ -8432,35 +8417,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <f>B9+B10+B11</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>C9+C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>D9+D10+D11</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>E9+E10+E11</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>F9+F10+F11</f>
         <v/>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="30">
         <f>G9+G10+G11</f>
         <v/>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="30">
         <f>H9+H10+H11</f>
         <v/>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="30">
         <f>I9+I10+I11</f>
         <v/>
       </c>
@@ -8471,35 +8456,35 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>B12-B14</f>
         <v/>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>C12-C14</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>D12-D14</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>E12*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>F12*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>G12*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <f>H12*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="30">
         <f>I12*Assumptions!$B$7</f>
         <v/>
       </c>
@@ -8522,23 +8507,23 @@
         <f>Assumptions!$B$67</f>
         <v/>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="31">
         <f>I12-I13</f>
         <v/>
       </c>

--- a/engine/scem_study/SCEM_Valuation_Model_06082026_public.xlsx
+++ b/engine/scem_study/SCEM_Valuation_Model_06082026_public.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,6 +158,7 @@
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -954,10 +955,10 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>2285.624</v>
-      </c>
-      <c r="C5" s="30">
-        <f>Assumptions!$B$69-C6-C7</f>
+        <v>1456.3910856</v>
+      </c>
+      <c r="C5" s="9">
+        <f>Assumptions!$B$97</f>
         <v/>
       </c>
       <c r="D5" s="30">
@@ -1029,7 +1030,7 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>1078</v>
+        <v>1333.45762648</v>
       </c>
       <c r="C7" s="30">
         <f>Assumptions!$B$59/1.25</f>
@@ -2262,7 +2263,7 @@
       <c r="B5" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
@@ -2292,7 +2293,7 @@
       <c r="B6" s="23" t="n">
         <v>62</v>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
@@ -2400,84 +2401,84 @@
       <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>Market panel verdict (Egypt)</t>
         </is>
       </c>
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>PASS — skill +0.0158, 90% interval [0.009, 0.022]</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>This name's verdict</t>
         </is>
       </c>
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>PARITY at every bootstrap block size {2,3,4}</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>This name's CRPS skill vs a random walk</t>
         </is>
       </c>
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>-0.1276 — BELOW zero</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>Coverage 50 / 80 / 90</t>
         </is>
       </c>
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>0.76 / 0.82 / 0.94 against nominal 0.50 / 0.80 / 0.90 — OVER-COVERED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>Cone width versus the benchmark</t>
         </is>
       </c>
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>4.71x</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="B18" s="41" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>SCEM prints an unchanged close on 29.3% of sessions, 3.4x the Egyptian panel median and 2nd thinnest of 33 names. On such a series the benchmark's own volatility estimate collapses in quiet quarters.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>Consequence</t>
         </is>
       </c>
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>The map is ILLUSTRATIVE ONLY. It is materially too wide and must not be read with the confidence of a calibrated name.</t>
         </is>
@@ -2538,7 +2539,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Explicit WACC (rows) × terminal growth (columns) — fair value per share (EGP)</t>
         </is>
@@ -2574,106 +2575,106 @@
     </row>
     <row r="6">
       <c r="A6" s="24" t="n">
-        <v>0.2529921630262293</v>
+        <v>0.2524268375532941</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>47.85239987575165</v>
+        <v>69.33880928933149</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>46.42807849453837</v>
+        <v>71.54122910452247</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>44.78777410811193</v>
+        <v>74.05293194356118</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>42.88206844733539</v>
+        <v>76.94556687941297</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>40.64506858524987</v>
+        <v>80.31463272222348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="24" t="n">
-        <v>0.2679921630262292</v>
+        <v>0.2674268375532941</v>
       </c>
       <c r="B7" s="18" t="n">
-        <v>47.27776652657919</v>
+        <v>68.42176777405973</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>45.88984005753007</v>
+        <v>70.56825147566461</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>44.29142556215732</v>
+        <v>73.0161404192561</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>42.4343627432738</v>
+        <v>75.8352594025983</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>40.25443599024933</v>
+        <v>79.11867568796789</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="24" t="n">
-        <v>0.2829921630262293</v>
+        <v>0.2824268375532941</v>
       </c>
       <c r="B8" s="18" t="n">
-        <v>46.72134103353847</v>
+        <v>67.53401996767445</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>45.36857897793945</v>
+        <v>69.62645385966159</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>43.81063846201682</v>
+        <v>72.01268121839149</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>42.0005747030714</v>
+        <v>74.76076415537712</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>39.87579279659943</v>
+        <v>77.96142047640899</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="24" t="n">
-        <v>0.2979921630262293</v>
+        <v>0.2974268375532941</v>
       </c>
       <c r="B9" s="18" t="n">
-        <v>46.18237106147301</v>
+        <v>66.67435112181579</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>44.8635952566741</v>
+        <v>68.71454137432963</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>43.34477302237466</v>
+        <v>71.04116801667909</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>41.58013443704983</v>
+        <v>73.72058944509278</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>39.50865109765196</v>
+        <v>76.84125261076062</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="24" t="n">
-        <v>0.3129921630262292</v>
+        <v>0.312426837553294</v>
       </c>
       <c r="B10" s="18" t="n">
-        <v>45.66014248947234</v>
+        <v>65.84160831557476</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>44.37422440920808</v>
+        <v>67.83128509639823</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>42.89322186668822</v>
+        <v>70.10028516345817</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>41.17250085938183</v>
+        <v>72.71331968570379</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>39.1525475625393</v>
+        <v>75.75664005208257</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>NET CASH — the largest single uncertainty, now sensitised</t>
         </is>
@@ -2683,50 +2684,50 @@
       <c r="A13" s="6" t="inlineStr"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>3,430</t>
+          <t>4,894</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>4,180</t>
+          <t>5,644</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>4,930</t>
+          <t>6,394</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>5,680</t>
+          <t>7,144</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>6,430</t>
+          <t>7,894</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>Fair value per share (EGP)</t>
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>38.05937986712988</v>
+        <v>66.26142262350457</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>40.93500916457335</v>
+        <v>69.13705192094802</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>43.81063846201682</v>
+        <v>72.01268121839149</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>46.68626775946028</v>
+        <v>74.88831051583496</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>49.56189705690375</v>
+        <v>77.76393981327843</v>
       </c>
     </row>
     <row r="16">
@@ -2744,7 +2745,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Beta — fair value per share (EGP)</t>
         </is>
@@ -2779,29 +2780,29 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>Fair value</t>
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>48.91357507019821</v>
+        <v>83.08174660985894</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>46.08776877600348</v>
+        <v>76.9482135066681</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>45.63025299419375</v>
+        <v>75.95598513270313</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>43.81063846201682</v>
+        <v>72.01268121839149</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>41.12064739648515</v>
+        <v>66.19456800863833</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>EBITDA margin shift — fair value per share (EGP)</t>
         </is>
@@ -2836,25 +2837,25 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>Fair value</t>
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>35.56710249338433</v>
+        <v>63.6256693590984</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>39.67644904785723</v>
+        <v>67.80588474043029</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>43.81063846201682</v>
+        <v>72.01268121839149</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>47.67735945226617</v>
+        <v>75.50881272014838</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>49.7950196365083</v>
+        <v>78.14817000538623</v>
       </c>
     </row>
     <row r="28">
@@ -4148,7 +4149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4239,16 +4240,6 @@
         <v>0.225</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Effective tax rate (historical closure)</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -4337,130 +4328,135 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Specific thermal energy</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="n">
-        <v>3.4</v>
+          <t>Materials, fuel, power, packing (note 24)</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>3592.466202</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>GJ/t clinker</t>
+          <t>EGP mn, FY2025</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Delivered fuel cost</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n">
-        <v>4</v>
+          <t>Transport, loading and export (notes 24, 25)</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>770.524093</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>USD/GJ</t>
+          <t>EGP mn, FY2025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Specific electrical energy</t>
+          <t>Fixed cash cost (the rest of notes 24, 25, 26)</t>
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>100</v>
+        <v>1270.954249</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>kWh/t cement</t>
+          <t>EGP mn, FY2025</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Industrial electricity tariff</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>2.6</v>
+          <t>Dollar-linked share of the materials line</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>0.484</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>EGP/kWh</t>
+          <t>ESTIMATED — the accounts do not split it</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Raw materials &amp; quarrying</t>
+          <t>Gross fixed assets (note 4)</t>
         </is>
       </c>
       <c r="B20" s="23" t="n">
-        <v>190</v>
+        <v>3140.855154</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>EGP/t cement</t>
+          <t>EGP mn, 31-Dec-2025</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="n">
-        <v>55</v>
+          <t>Weighted depreciation rate (note 3/2 on note 4)</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>0.038626</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>EGP/t bagged</t>
+          <t>straight-line</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bagged share of despatches</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n">
-        <v>0.7</v>
+          <t>Capex run rate (cash-flow statements)</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>303.211</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn/yr</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Distribution &amp; selling</t>
+          <t>Cash, reviewed sheet 31-Mar-2026</t>
         </is>
       </c>
       <c r="B23" s="23" t="n">
-        <v>250</v>
+        <v>5801.981716</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>EGP/t cement</t>
+          <t>EGP mn</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fixed cash cost</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n">
-        <v>14.6</v>
+          <t>Lease liabilities, 31-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>152.709964</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>USD/t of capacity</t>
+          <t>EGP mn</t>
         </is>
       </c>
     </row>
@@ -4687,50 +4683,6 @@
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>D&amp;A / revenue</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="C36" s="20" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="E36" s="20" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="F36" s="20" t="n">
-        <v>0.042</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Capex / revenue</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C37" s="20" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="F37" s="20" t="n">
-        <v>0.045</v>
-      </c>
-    </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -4793,16 +4745,6 @@
       </c>
       <c r="B41" s="20" t="n">
         <v>0.6</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Yield on cash, FY2025</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
-        <v>0.21</v>
       </c>
     </row>
     <row r="44">
@@ -4877,7 +4819,7 @@
         </is>
       </c>
       <c r="B50" s="21" t="n">
-        <v>36.8</v>
+        <v>137.565888</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
@@ -4967,7 +4909,7 @@
         </is>
       </c>
       <c r="B59" s="23" t="n">
-        <v>3850</v>
+        <v>4762.348666</v>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
@@ -4982,7 +4924,7 @@
         </is>
       </c>
       <c r="B60" s="23" t="n">
-        <v>5240</v>
+        <v>6020.338736</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
@@ -5012,7 +4954,7 @@
         </is>
       </c>
       <c r="B62" s="23" t="n">
-        <v>4280</v>
+        <v>4285.470153</v>
       </c>
     </row>
     <row r="63">
@@ -5022,7 +4964,7 @@
         </is>
       </c>
       <c r="B63" s="23" t="n">
-        <v>6420</v>
+        <v>6428.011851</v>
       </c>
     </row>
     <row r="64">
@@ -5032,7 +4974,7 @@
         </is>
       </c>
       <c r="B64" s="23" t="n">
-        <v>9090</v>
+        <v>9089.149688</v>
       </c>
     </row>
     <row r="65">
@@ -5042,7 +4984,7 @@
         </is>
       </c>
       <c r="B65" s="23" t="n">
-        <v>-121.42</v>
+        <v>-117.581612</v>
       </c>
     </row>
     <row r="66">
@@ -5052,7 +4994,7 @@
         </is>
       </c>
       <c r="B66" s="23" t="n">
-        <v>3070</v>
+        <v>3072.361811</v>
       </c>
     </row>
     <row r="67">
@@ -5062,17 +5004,7 @@
         </is>
       </c>
       <c r="B67" s="23" t="n">
-        <v>2290</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>FY2024 EBITDA (disclosed anchor)</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="n">
-        <v>1590</v>
+        <v>2284.539004</v>
       </c>
     </row>
     <row r="69">
@@ -5095,16 +5027,6 @@
         <v>1610.86</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>FY2023 treasury income</t>
-        </is>
-      </c>
-      <c r="B71" s="23" t="n">
-        <v>198</v>
-      </c>
-    </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -5148,36 +5070,6 @@
         <is>
           <t>mn</t>
         </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>D&amp;A / revenue, FY2023</t>
-        </is>
-      </c>
-      <c r="B75" s="20" t="n">
-        <v>0.094</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>D&amp;A / revenue, FY2024</t>
-        </is>
-      </c>
-      <c r="B76" s="20" t="n">
-        <v>0.062</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>D&amp;A / revenue, FY2025</t>
-        </is>
-      </c>
-      <c r="B77" s="20" t="n">
-        <v>0.046</v>
       </c>
     </row>
     <row r="79">
@@ -5329,45 +5221,100 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sinai White disposal — EUR consideration</t>
-        </is>
-      </c>
-      <c r="B92" s="21" t="n">
-        <v>30</v>
+          <t>Gain on sale of investments, FY2024 (as filed)</t>
+        </is>
+      </c>
+      <c r="B92" s="23" t="n">
+        <v>1517.386642</v>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>EUR mn</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>EGP per EUR at completion</t>
-        </is>
-      </c>
-      <c r="B93" s="21" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Aug-2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Sinai White stake — carrying value</t>
-        </is>
-      </c>
-      <c r="B94" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
           <t>EGP mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Operating assets at 31-Dec-2024 (fixed assets net, intangibles, CWIP)</t>
+        </is>
+      </c>
+      <c r="B97" s="23" t="n">
+        <v>1533.043248</v>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn, as filed</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>THE FILED HISTORICALS — AUDITED STATEMENTS, NOTHING SOLVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; amortisation</t>
+        </is>
+      </c>
+      <c r="B100" s="23" t="n">
+        <v>87.229927</v>
+      </c>
+      <c r="C100" s="23" t="n">
+        <v>90.750017</v>
+      </c>
+      <c r="D100" s="23" t="n">
+        <v>122.558896</v>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn, FY2023-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>EBIT (operating profit plus the finance charge inside it)</t>
+        </is>
+      </c>
+      <c r="B101" s="23" t="n">
+        <v>196.326392</v>
+      </c>
+      <c r="C101" s="23" t="n">
+        <v>1494.712536</v>
+      </c>
+      <c r="D101" s="23" t="n">
+        <v>3332.646248</v>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn, FY2023-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Interest and investment income</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="n">
+        <v>6.973315</v>
+      </c>
+      <c r="C102" s="23" t="n">
+        <v>29.990318</v>
+      </c>
+      <c r="D102" s="23" t="n">
+        <v>171.609009</v>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn, FY2023-25</t>
         </is>
       </c>
     </row>
@@ -6163,155 +6110,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Thermal fuel</t>
+          <t>Materials, fuel, power and packing (note 24)</t>
         </is>
       </c>
       <c r="B23" s="30">
-        <f>Assumptions!$B$16*B9*Assumptions!$B$17*B16</f>
+        <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*B16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$B$33/Assumptions!$B$33)</f>
         <v/>
       </c>
       <c r="C23" s="30">
-        <f>Assumptions!$B$16*C9*Assumptions!$B$17*C16</f>
+        <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*C16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$C$33/Assumptions!$B$33)</f>
         <v/>
       </c>
       <c r="D23" s="30">
-        <f>Assumptions!$B$16*D9*Assumptions!$B$17*D16</f>
+        <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*D16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$D$33/Assumptions!$B$33)</f>
         <v/>
       </c>
       <c r="E23" s="30">
-        <f>Assumptions!$B$16*E9*Assumptions!$B$17*E16</f>
+        <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*E16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$E$33/Assumptions!$B$33)</f>
         <v/>
       </c>
       <c r="F23" s="30">
-        <f>Assumptions!$B$16*F9*Assumptions!$B$17*F16</f>
+        <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*F16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$F$33/Assumptions!$B$33)</f>
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>Assumptions!$B$16*G9*Assumptions!$B$17*G16</f>
+        <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*G16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$G$33/Assumptions!$B$33)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Electrical power</t>
+          <t>Transport, loading and export (notes 24 and 25)</t>
         </is>
       </c>
       <c r="B24" s="30">
-        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$B$33</f>
+        <f>Assumptions!$B$17/$B$10*Assumptions!$B$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="C24" s="30">
-        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$C$33</f>
+        <f>Assumptions!$B$17/$B$10*Assumptions!$C$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="D24" s="30">
-        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$D$33</f>
+        <f>Assumptions!$B$17/$B$10*Assumptions!$D$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="E24" s="30">
-        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$E$33</f>
+        <f>Assumptions!$B$17/$B$10*Assumptions!$E$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="F24" s="30">
-        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$F$33</f>
+        <f>Assumptions!$B$17/$B$10*Assumptions!$F$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>Assumptions!$B$18*Assumptions!$B$19*Assumptions!$G$33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Raw materials &amp; quarrying</t>
-        </is>
-      </c>
-      <c r="B25" s="30">
-        <f>Assumptions!$B$20*Assumptions!$B$33</f>
-        <v/>
-      </c>
-      <c r="C25" s="30">
-        <f>Assumptions!$B$20*Assumptions!$C$33</f>
-        <v/>
-      </c>
-      <c r="D25" s="30">
-        <f>Assumptions!$B$20*Assumptions!$D$33</f>
-        <v/>
-      </c>
-      <c r="E25" s="30">
-        <f>Assumptions!$B$20*Assumptions!$E$33</f>
-        <v/>
-      </c>
-      <c r="F25" s="30">
-        <f>Assumptions!$B$20*Assumptions!$F$33</f>
-        <v/>
-      </c>
-      <c r="G25" s="30">
-        <f>Assumptions!$B$20*Assumptions!$G$33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B26" s="30">
-        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$B$33</f>
-        <v/>
-      </c>
-      <c r="C26" s="30">
-        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$C$33</f>
-        <v/>
-      </c>
-      <c r="D26" s="30">
-        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$D$33</f>
-        <v/>
-      </c>
-      <c r="E26" s="30">
-        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$E$33</f>
-        <v/>
-      </c>
-      <c r="F26" s="30">
-        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$F$33</f>
-        <v/>
-      </c>
-      <c r="G26" s="30">
-        <f>Assumptions!$B$21*Assumptions!$B$22*Assumptions!$G$33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Distribution &amp; selling</t>
-        </is>
-      </c>
-      <c r="B27" s="30">
-        <f>Assumptions!$B$23*Assumptions!$B$33</f>
-        <v/>
-      </c>
-      <c r="C27" s="30">
-        <f>Assumptions!$B$23*Assumptions!$C$33</f>
-        <v/>
-      </c>
-      <c r="D27" s="30">
-        <f>Assumptions!$B$23*Assumptions!$D$33</f>
-        <v/>
-      </c>
-      <c r="E27" s="30">
-        <f>Assumptions!$B$23*Assumptions!$E$33</f>
-        <v/>
-      </c>
-      <c r="F27" s="30">
-        <f>Assumptions!$B$23*Assumptions!$F$33</f>
-        <v/>
-      </c>
-      <c r="G27" s="30">
-        <f>Assumptions!$B$23*Assumptions!$G$33</f>
+        <f>Assumptions!$B$17/$B$10*Assumptions!$G$33/Assumptions!$B$33</f>
         <v/>
       </c>
     </row>
@@ -6322,27 +6176,27 @@
         </is>
       </c>
       <c r="B28" s="31">
-        <f>SUM(B23:B27)</f>
+        <f>B23+B24</f>
         <v/>
       </c>
       <c r="C28" s="31">
-        <f>SUM(C23:C27)</f>
+        <f>C23+C24</f>
         <v/>
       </c>
       <c r="D28" s="31">
-        <f>SUM(D23:D27)</f>
+        <f>D23+D24</f>
         <v/>
       </c>
       <c r="E28" s="31">
-        <f>SUM(E23:E27)</f>
+        <f>E23+E24</f>
         <v/>
       </c>
       <c r="F28" s="31">
-        <f>SUM(F23:F27)</f>
+        <f>F23+F24</f>
         <v/>
       </c>
       <c r="G28" s="31">
-        <f>SUM(G23:G27)</f>
+        <f>G23+G24</f>
         <v/>
       </c>
     </row>
@@ -6431,27 +6285,27 @@
         </is>
       </c>
       <c r="B33" s="30">
-        <f>Assumptions!$B$24*B8*Assumptions!$B$9*Assumptions!$B$33</f>
+        <f>Assumptions!$B$18*Assumptions!$B$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="C33" s="30">
-        <f>Assumptions!$B$24*C8*Assumptions!$B$9*Assumptions!$C$33</f>
+        <f>Assumptions!$B$18*Assumptions!$C$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="D33" s="30">
-        <f>Assumptions!$B$24*D8*Assumptions!$B$9*Assumptions!$D$33</f>
+        <f>Assumptions!$B$18*Assumptions!$D$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="E33" s="30">
-        <f>Assumptions!$B$24*E8*Assumptions!$B$9*Assumptions!$E$33</f>
+        <f>Assumptions!$B$18*Assumptions!$E$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="F33" s="30">
-        <f>Assumptions!$B$24*F8*Assumptions!$B$9*Assumptions!$F$33</f>
+        <f>Assumptions!$B$18*Assumptions!$F$33/Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>Assumptions!$B$24*G8*Assumptions!$B$9*Assumptions!$G$33</f>
+        <f>Assumptions!$B$18*Assumptions!$G$33/Assumptions!$B$33</f>
         <v/>
       </c>
     </row>
@@ -7293,23 +7147,23 @@
         </is>
       </c>
       <c r="B8" s="30">
-        <f>B5*Assumptions!$B$36</f>
+        <f>B21*Assumptions!$B$21</f>
         <v/>
       </c>
       <c r="C8" s="30">
-        <f>C5*Assumptions!$C$36</f>
+        <f>C21*Assumptions!$B$21</f>
         <v/>
       </c>
       <c r="D8" s="30">
-        <f>D5*Assumptions!$D$36</f>
+        <f>D21*Assumptions!$B$21</f>
         <v/>
       </c>
       <c r="E8" s="30">
-        <f>E5*Assumptions!$E$36</f>
+        <f>E21*Assumptions!$B$21</f>
         <v/>
       </c>
       <c r="F8" s="30">
-        <f>F5*Assumptions!$F$36</f>
+        <f>F21*Assumptions!$B$21</f>
         <v/>
       </c>
     </row>
@@ -7401,23 +7255,23 @@
         </is>
       </c>
       <c r="B12" s="30">
-        <f>B5*Assumptions!$B$37</f>
+        <f>B20</f>
         <v/>
       </c>
       <c r="C12" s="30">
-        <f>C5*Assumptions!$C$37</f>
+        <f>C20</f>
         <v/>
       </c>
       <c r="D12" s="30">
-        <f>D5*Assumptions!$D$37</f>
+        <f>D20</f>
         <v/>
       </c>
       <c r="E12" s="30">
-        <f>E5*Assumptions!$E$37</f>
+        <f>E20</f>
         <v/>
       </c>
       <c r="F12" s="30">
-        <f>F5*Assumptions!$F$37</f>
+        <f>F20</f>
         <v/>
       </c>
     </row>
@@ -7451,27 +7305,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Net reinvestment  (growth ÷ terminal ROIC)</t>
+          <t>Net capital charge  (capex + working capital − depreciation)</t>
         </is>
       </c>
       <c r="B14" s="30">
-        <f>MAX(B11-$B$23,0)/$B$24</f>
+        <f>B12+B13-B8</f>
         <v/>
       </c>
       <c r="C14" s="30">
-        <f>MAX(C11-B11,0)/$B$24</f>
+        <f>C12+C13-C8</f>
         <v/>
       </c>
       <c r="D14" s="30">
-        <f>MAX(D11-C11,0)/$B$24</f>
+        <f>D12+D13-D8</f>
         <v/>
       </c>
       <c r="E14" s="30">
-        <f>MAX(E11-D11,0)/$B$24</f>
+        <f>E12+E13-E8</f>
         <v/>
       </c>
       <c r="F14" s="30">
-        <f>MAX(F11-E11,0)/$B$24</f>
+        <f>F12+F13-F8</f>
         <v/>
       </c>
     </row>
@@ -7482,23 +7336,23 @@
         </is>
       </c>
       <c r="B15" s="31">
-        <f>(B11-B14)*(1-Assumptions!$B$56)</f>
+        <f>(B11+B8-B12-B13)*(1-Assumptions!$B$56)</f>
         <v/>
       </c>
       <c r="C15" s="31">
-        <f>C11-C14</f>
+        <f>C11+C8-C12-C13</f>
         <v/>
       </c>
       <c r="D15" s="31">
-        <f>D11-D14</f>
+        <f>D11+D8-D12-D13</f>
         <v/>
       </c>
       <c r="E15" s="31">
-        <f>E11-E14</f>
+        <f>E11+E8-E12-E13</f>
         <v/>
       </c>
       <c r="F15" s="31">
-        <f>F11-F14</f>
+        <f>F11+F8-F12-F13</f>
         <v/>
       </c>
     </row>
@@ -7610,17 +7464,59 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Memo: capital expenditure, on the company's own run rate</t>
+        </is>
+      </c>
+      <c r="B20" s="30">
+        <f>Assumptions!$B$22*Assumptions!$C$33/Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="C20" s="30">
+        <f>Assumptions!$B$22*Assumptions!$D$33/Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="D20" s="30">
+        <f>Assumptions!$B$22*Assumptions!$E$33/Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="E20" s="30">
+        <f>Assumptions!$B$22*Assumptions!$F$33/Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="F20" s="30">
+        <f>Assumptions!$B$22*Assumptions!$G$33/Assumptions!$B$33</f>
+        <v/>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>TERMINAL BLOCK</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
+      <c r="B21" s="36">
+        <f>Assumptions!$B$20+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="36">
+        <f>B21+C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="36">
+        <f>C21+D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="36">
+        <f>D21+E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="36">
+        <f>E21+F20</f>
+        <v/>
+      </c>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n"/>
     </row>
@@ -7660,11 +7556,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Reinvestment rate  (g ÷ ROIC)</t>
-        </is>
-      </c>
-      <c r="B25" s="12">
-        <f>Assumptions!$B$55/B24</f>
+          <t>Maintenance at current cost  (invested capital / life)</t>
+        </is>
+      </c>
+      <c r="B25" s="30">
+        <f>B22/B45</f>
         <v/>
       </c>
     </row>
@@ -7675,7 +7571,7 @@
         </is>
       </c>
       <c r="B26" s="30">
-        <f>B28*(1-B25)/($C$53-Assumptions!$B$55)</f>
+        <f>B48*(1+Assumptions!$B$55)/($C$53-Assumptions!$B$55)</f>
         <v/>
       </c>
     </row>
@@ -7762,22 +7658,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cash at the valuation date</t>
+          <t>Cash, reviewed sheet at 31 March 2026</t>
         </is>
       </c>
       <c r="B34" s="30">
-        <f>'Balance Sheet'!D7+B15/(1-Assumptions!$B$56)*Assumptions!$B$56</f>
+        <f>Assumptions!$B$23+B15/(1-Assumptions!$B$56)*(Assumptions!$B$56-0.25)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Less gross debt</t>
+          <t>Less lease liabilities (there are no bank borrowings)</t>
         </is>
       </c>
       <c r="B35" s="30">
-        <f>-Assumptions!$B$50</f>
+        <f>-Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
@@ -7809,7 +7705,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B38" s="36">
+      <c r="B38" s="37">
         <f>Assumptions!$B$6</f>
         <v/>
       </c>
@@ -7889,6 +7785,10 @@
           <t>Cost of equity  (rf* + β × ERP)</t>
         </is>
       </c>
+      <c r="B45" s="33">
+        <f>1/Assumptions!$B$21</f>
+        <v/>
+      </c>
       <c r="C45" s="35">
         <f>C44+Assumptions!$B$48*Assumptions!$B$47</f>
         <v/>
@@ -7900,8 +7800,23 @@
           <t>WACC — explicit window</t>
         </is>
       </c>
-      <c r="C46" s="37">
+      <c r="B46" s="30">
+        <f>DCF!F8*(1+Assumptions!$B$55)</f>
+        <v/>
+      </c>
+      <c r="C46" s="38">
         <f>(1-C49)*C45+C49*C48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Working capital charged with inflation</t>
+        </is>
+      </c>
+      <c r="B47" s="30">
+        <f>Assumptions!$B$64*Assumptions!$B$40*Assumptions!$B$55</f>
         <v/>
       </c>
     </row>
@@ -7911,6 +7826,10 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
+      <c r="B48" s="30">
+        <f>B28+B46-B25-B47</f>
+        <v/>
+      </c>
       <c r="C48" s="35">
         <f>Assumptions!$B$49*(1-Assumptions!$B$7)</f>
         <v/>
@@ -7922,7 +7841,7 @@
           <t>Debt weight  D/(D+E)</t>
         </is>
       </c>
-      <c r="C49" s="38">
+      <c r="C49" s="39">
         <f>Assumptions!$B$50/(Assumptions!$B$50+C50)</f>
         <v/>
       </c>
@@ -7966,7 +7885,7 @@
           <t>WACC — terminal</t>
         </is>
       </c>
-      <c r="C53" s="37">
+      <c r="C53" s="38">
         <f>(1-Assumptions!$B$54)*C51+Assumptions!$B$54*C52</f>
         <v/>
       </c>
@@ -8261,16 +8180,16 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B8" s="30">
-        <f>B5*Assumptions!$B$75</f>
-        <v/>
-      </c>
-      <c r="C8" s="30">
-        <f>C5*Assumptions!$B$76</f>
-        <v/>
-      </c>
-      <c r="D8" s="30">
-        <f>D5*Assumptions!$B$77</f>
+      <c r="B8" s="9">
+        <f>Assumptions!$B$100</f>
+        <v/>
+      </c>
+      <c r="C8" s="9">
+        <f>Assumptions!$C$100</f>
+        <v/>
+      </c>
+      <c r="D8" s="9">
+        <f>Assumptions!$D$100</f>
         <v/>
       </c>
       <c r="E8" s="9">
@@ -8300,16 +8219,16 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="30">
-        <f>B14-B10</f>
-        <v/>
-      </c>
-      <c r="C9" s="30">
-        <f>Assumptions!$B$68-C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="30">
-        <f>D14/(1-Assumptions!$B$8)-D10</f>
+      <c r="B9" s="9">
+        <f>Assumptions!$B$101</f>
+        <v/>
+      </c>
+      <c r="C9" s="9">
+        <f>Assumptions!$C$101</f>
+        <v/>
+      </c>
+      <c r="D9" s="9">
+        <f>Assumptions!$D$101</f>
         <v/>
       </c>
       <c r="E9" s="30">
@@ -8340,15 +8259,15 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>Assumptions!$B$71</f>
-        <v/>
-      </c>
-      <c r="C10" s="30">
-        <f>Assumptions!$B$59/1.25*0.9*Assumptions!$B$42</f>
-        <v/>
-      </c>
-      <c r="D10" s="30">
-        <f>(Assumptions!$B$59+Assumptions!$B$59/1.25)/2*Assumptions!$B$42</f>
+        <f>Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="C10" s="9">
+        <f>Assumptions!$C$102</f>
+        <v/>
+      </c>
+      <c r="D10" s="9">
+        <f>Assumptions!$D$102</f>
         <v/>
       </c>
       <c r="E10" s="30">
@@ -8382,8 +8301,8 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="C11" s="30">
-        <f>Assumptions!$B$92*Assumptions!$B$93-Assumptions!$B$94</f>
+      <c r="C11" s="9">
+        <f>Assumptions!$B$92</f>
         <v/>
       </c>
       <c r="D11" s="30">
